--- a/360MasterData_CH.xlsx
+++ b/360MasterData_CH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4B1511D-F514-46D1-B127-4EA0A890B4E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23EEE9B-88B9-4305-8A72-7BDA6B64079F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -1043,13 +1043,7 @@
     <t>Text</t>
   </si>
   <si>
-    <t>Welcome to ILLUS 360° Virtual tour</t>
-  </si>
-  <si>
     <t>Audio URL</t>
-  </si>
-  <si>
-    <t>Premium quality, High CRI, Wide variety of lumen options, Flicker-Free performance.</t>
   </si>
   <si>
     <t>[https://cdn.salla.sa/zKxdl/90be94ad-1350-4999-9fe4-2238aab65b76-1000x1000-yUrZlnrqk1FR3zH01iYKvSsEnlHferxfngAiPLB6.jpg],[https://cdn.apartmenttherapy.info/image/upload/v1554217999/at/house%20tours%20stock%20archive/7f6d6749cdc500dd3a8c93d2e1c6ad6aa7be7dec.jpg],[https://cdn.salla.sa/zKxdl/e8969cdb-689b-4fa2-acec-32d62f1372f9-1000x1000-Vv1rVdmcTYfMxVrzGFm2WrtJMe9hOB1Lzy3qkL1W.jpg],[https://cdn.salla.sa/zKxdl/c1e159c4-d295-41a5-bec3-ff3afc60f084-1000x1000-5oPAkXLZo1O1vCXlugIxp1KA92G4pY4NTg3bstIY.jpg],[https://cdn.salla.sa/zKxdl/692c74f8-1453-47d9-abdf-fa262b68686b-1000x1000-Yqc9OtitlmvNpYBlKy2VGbO8Yg5WvfNLANfYy94L.jpg]</t>
@@ -1559,6 +1553,12 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/Answer01_CH.mp3</t>
+  </si>
+  <si>
+    <t>欢迎来到ILLUS 360°虚拟参观</t>
+  </si>
+  <si>
+    <t>优质、高 CRI、多种流明选择、无闪烁性能。</t>
   </si>
 </sst>
 </file>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="2" spans="1:28" ht="18.3" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -2793,7 +2793,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>188</v>
@@ -2847,7 +2847,7 @@
         <v>301</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="X2" s="10" t="b">
         <v>1</v>
@@ -2856,7 +2856,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="68" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="AA2" s="12">
         <v>45750</v>
@@ -2867,7 +2867,7 @@
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -2879,7 +2879,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>179</v>
@@ -2942,7 +2942,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="76" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="AA3" s="12">
         <v>45750</v>
@@ -2953,7 +2953,7 @@
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -2965,7 +2965,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>178</v>
@@ -3034,7 +3034,7 @@
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -3046,7 +3046,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>176</v>
@@ -3116,7 +3116,7 @@
     </row>
     <row r="6" spans="1:28" ht="20.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
@@ -3128,7 +3128,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>177</v>
@@ -3198,7 +3198,7 @@
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>50</v>
@@ -3210,7 +3210,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>180</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>50</v>
@@ -3292,7 +3292,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>201</v>
@@ -3346,7 +3346,7 @@
         <v>34</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="X8" s="15" t="b">
         <v>0</v>
@@ -3364,7 +3364,7 @@
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>50</v>
@@ -3376,7 +3376,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>175</v>
@@ -3448,7 +3448,7 @@
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>50</v>
@@ -3460,7 +3460,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>221</v>
@@ -3532,7 +3532,7 @@
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>50</v>
@@ -3544,7 +3544,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F11" s="38" t="s">
         <v>220</v>
@@ -3614,7 +3614,7 @@
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>50</v>
@@ -3626,7 +3626,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>181</v>
@@ -3698,7 +3698,7 @@
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>78</v>
@@ -3710,7 +3710,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>182</v>
@@ -3782,7 +3782,7 @@
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>78</v>
@@ -3794,7 +3794,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>183</v>
@@ -3866,7 +3866,7 @@
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>78</v>
@@ -3878,7 +3878,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>184</v>
@@ -3950,7 +3950,7 @@
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>27</v>
@@ -3962,7 +3962,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>185</v>
@@ -4034,7 +4034,7 @@
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>27</v>
@@ -4046,7 +4046,7 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>186</v>
@@ -4118,7 +4118,7 @@
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>27</v>
@@ -4130,7 +4130,7 @@
         <v>17</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>187</v>
@@ -4202,7 +4202,7 @@
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>99</v>
@@ -4214,7 +4214,7 @@
         <v>18</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>189</v>
@@ -4286,7 +4286,7 @@
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>99</v>
@@ -4298,7 +4298,7 @@
         <v>19</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>190</v>
@@ -4370,7 +4370,7 @@
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>99</v>
@@ -4382,7 +4382,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>191</v>
@@ -4454,7 +4454,7 @@
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>99</v>
@@ -4466,7 +4466,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>192</v>
@@ -4538,7 +4538,7 @@
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>99</v>
@@ -4550,7 +4550,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>193</v>
@@ -4624,7 +4624,7 @@
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>99</v>
@@ -4636,7 +4636,7 @@
         <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>207</v>
@@ -4708,7 +4708,7 @@
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>99</v>
@@ -4720,7 +4720,7 @@
         <v>24</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>202</v>
@@ -4792,7 +4792,7 @@
     </row>
     <row r="26" spans="1:28" ht="12" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>99</v>
@@ -4804,7 +4804,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>194</v>
@@ -4876,7 +4876,7 @@
     </row>
     <row r="27" spans="1:28" ht="12" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>99</v>
@@ -4888,7 +4888,7 @@
         <v>26</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>203</v>
@@ -4960,7 +4960,7 @@
     </row>
     <row r="28" spans="1:28" ht="12" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>99</v>
@@ -4972,7 +4972,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>204</v>
@@ -5044,7 +5044,7 @@
     </row>
     <row r="29" spans="1:28" ht="12" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>99</v>
@@ -5056,7 +5056,7 @@
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>205</v>
@@ -5128,7 +5128,7 @@
     </row>
     <row r="30" spans="1:28" ht="12" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>99</v>
@@ -5140,7 +5140,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>206</v>
@@ -5212,7 +5212,7 @@
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>99</v>
@@ -5224,7 +5224,7 @@
         <v>30</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>208</v>
@@ -5296,7 +5296,7 @@
     </row>
     <row r="32" spans="1:28" ht="12" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>99</v>
@@ -5308,7 +5308,7 @@
         <v>31</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>209</v>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="N3" s="35"/>
       <c r="O3" s="57" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="Q3"/>
     </row>
@@ -23037,13 +23037,13 @@
         <v>303</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="F2" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>151</v>
@@ -23055,7 +23055,7 @@
         <v>173</v>
       </c>
       <c r="J2" s="45" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="K2" s="57" t="s">
         <v>279</v>
@@ -23072,13 +23072,13 @@
         <v>304</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F3" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G3" s="40" t="s">
         <v>154</v>
@@ -23090,7 +23090,7 @@
         <v>31</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="K3" s="57" t="s">
         <v>279</v>
@@ -23107,13 +23107,13 @@
         <v>306</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="F4" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G4" s="43" t="s">
         <v>151</v>
@@ -23142,13 +23142,13 @@
         <v>307</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G5" s="49" t="s">
         <v>151</v>
@@ -23177,13 +23177,13 @@
         <v>307</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G6" s="43" t="s">
         <v>151</v>
@@ -23212,13 +23212,13 @@
         <v>307</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="E7" s="40" t="s">
+        <v>367</v>
+      </c>
+      <c r="F7" s="77" t="s">
         <v>369</v>
-      </c>
-      <c r="F7" s="77" t="s">
-        <v>371</v>
       </c>
       <c r="G7" s="49" t="s">
         <v>151</v>
@@ -23247,13 +23247,13 @@
         <v>307</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G8" s="41" t="s">
         <v>154</v>
@@ -23265,7 +23265,7 @@
         <v>31</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="K8" s="57" t="s">
         <v>279</v>
@@ -23286,7 +23286,7 @@
         <v>156</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G9" s="49" t="s">
         <v>151</v>
@@ -23298,7 +23298,7 @@
         <v>31</v>
       </c>
       <c r="J9" s="51" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="K9" s="57" t="s">
         <v>279</v>
@@ -23319,7 +23319,7 @@
         <v>158</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G10" s="43" t="s">
         <v>151</v>
@@ -23352,7 +23352,7 @@
         <v>160</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G11" s="49" t="s">
         <v>151</v>
@@ -23385,7 +23385,7 @@
         <v>150</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G12" s="43" t="s">
         <v>151</v>
@@ -23418,7 +23418,7 @@
         <v>153</v>
       </c>
       <c r="F13" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G13" s="40" t="s">
         <v>154</v>
@@ -23451,7 +23451,7 @@
         <v>156</v>
       </c>
       <c r="F14" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>151</v>
@@ -23484,7 +23484,7 @@
         <v>158</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G15" s="49" t="s">
         <v>151</v>
@@ -23517,7 +23517,7 @@
         <v>160</v>
       </c>
       <c r="F16" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G16" s="43" t="s">
         <v>151</v>
@@ -23552,7 +23552,7 @@
         <v>150</v>
       </c>
       <c r="F17" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>151</v>
@@ -23587,7 +23587,7 @@
         <v>153</v>
       </c>
       <c r="F18" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G18" s="41" t="s">
         <v>154</v>
@@ -23620,7 +23620,7 @@
         <v>156</v>
       </c>
       <c r="F19" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G19" s="49" t="s">
         <v>151</v>
@@ -23653,7 +23653,7 @@
         <v>158</v>
       </c>
       <c r="F20" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G20" s="43" t="s">
         <v>151</v>
@@ -23688,7 +23688,7 @@
         <v>160</v>
       </c>
       <c r="F21" s="77" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="G21" s="49" t="s">
         <v>151</v>
@@ -23811,10 +23811,10 @@
         <v>253</v>
       </c>
       <c r="E2" s="68" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" s="70" t="s">
         <v>374</v>
-      </c>
-      <c r="F2" s="70" t="s">
-        <v>376</v>
       </c>
       <c r="G2" s="70" t="s">
         <v>263</v>
@@ -23836,13 +23836,13 @@
         <v>258</v>
       </c>
       <c r="E3" s="68" t="s">
+        <v>372</v>
+      </c>
+      <c r="F3" s="70" t="s">
         <v>374</v>
       </c>
-      <c r="F3" s="70" t="s">
-        <v>376</v>
-      </c>
       <c r="G3" s="70" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="H3" s="29"/>
     </row>
@@ -23860,10 +23860,10 @@
         <v>259</v>
       </c>
       <c r="E4" s="68" t="s">
+        <v>372</v>
+      </c>
+      <c r="F4" s="70" t="s">
         <v>374</v>
-      </c>
-      <c r="F4" s="70" t="s">
-        <v>376</v>
       </c>
       <c r="G4" s="70" t="s">
         <v>263</v>
@@ -24882,7 +24882,7 @@
         <v>315</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="D1" s="29" t="s">
         <v>135</v>
@@ -24893,13 +24893,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>316</v>
+        <v>376</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>318</v>
+        <v>377</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1">

--- a/360MasterData_CH.xlsx
+++ b/360MasterData_CH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D23EEE9B-88B9-4305-8A72-7BDA6B64079F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{972AFC57-21C7-422F-94D8-1D0259C1A7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -847,9 +847,6 @@
     <t>Answer Media URL</t>
   </si>
   <si>
-    <t>Illus Magnetic Track Light: 5 Common Questions</t>
-  </si>
-  <si>
     <t>Hotspot Icon URL</t>
   </si>
   <si>
@@ -860,12 +857,6 @@
   </si>
   <si>
     <t>Size:30px,Rotate X:68°,Y:0°,Z:0°,Perspective:160°,https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/NAVHST.svg</t>
-  </si>
-  <si>
-    <t>Illus Spot Light: 2 Common Questions</t>
-  </si>
-  <si>
-    <t>Hypnotek Diffucer: 10 Common Questions</t>
   </si>
   <si>
     <t>QNA</t>
@@ -1559,6 +1550,15 @@
   </si>
   <si>
     <t>优质、高 CRI、多种流明选择、无闪烁性能。</t>
+  </si>
+  <si>
+    <t>Illus 磁吸轨道灯：5 个常见问题</t>
+  </si>
+  <si>
+    <t>插图聚焦：2 个常见问题</t>
+  </si>
+  <si>
+    <t>Hypnotek 扩散器：10 个常见问题</t>
   </si>
 </sst>
 </file>
@@ -2781,7 +2781,7 @@
     </row>
     <row r="2" spans="1:28" ht="18.3" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -2793,13 +2793,13 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>188</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H2" s="5" t="s">
         <v>29</v>
@@ -2808,7 +2808,7 @@
         <v>1</v>
       </c>
       <c r="J2" s="62" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="K2" s="62" t="s">
         <v>173</v>
@@ -2844,10 +2844,10 @@
         <v>1</v>
       </c>
       <c r="V2" s="75" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="X2" s="10" t="b">
         <v>1</v>
@@ -2856,18 +2856,18 @@
         <v>1</v>
       </c>
       <c r="Z2" s="68" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="AA2" s="12">
         <v>45750</v>
       </c>
       <c r="AB2" s="72" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -2879,13 +2879,13 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>179</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>29</v>
@@ -2930,7 +2930,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="75" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="W3" s="11" t="s">
         <v>38</v>
@@ -2942,18 +2942,18 @@
         <v>1</v>
       </c>
       <c r="Z3" s="76" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="AA3" s="12">
         <v>45750</v>
       </c>
       <c r="AB3" s="72" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -2965,13 +2965,13 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>178</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>40</v>
@@ -3029,12 +3029,12 @@
         <v>45750</v>
       </c>
       <c r="AB4" s="72" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -3046,13 +3046,13 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>176</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>29</v>
@@ -3111,12 +3111,12 @@
         <v>45750</v>
       </c>
       <c r="AB5" s="72" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="20.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
@@ -3128,13 +3128,13 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>177</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>29</v>
@@ -3193,12 +3193,12 @@
         <v>45750</v>
       </c>
       <c r="AB6" s="72" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>50</v>
@@ -3210,13 +3210,13 @@
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>180</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>52</v>
@@ -3275,12 +3275,12 @@
         <v>45750</v>
       </c>
       <c r="AB7" s="72" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>50</v>
@@ -3292,13 +3292,13 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>201</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>29</v>
@@ -3346,7 +3346,7 @@
         <v>34</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="X8" s="15" t="b">
         <v>0</v>
@@ -3359,12 +3359,12 @@
         <v>45750</v>
       </c>
       <c r="AB8" s="71" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>50</v>
@@ -3376,13 +3376,13 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>175</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>29</v>
@@ -3443,12 +3443,12 @@
         <v>45750</v>
       </c>
       <c r="AB9" s="71" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>50</v>
@@ -3460,13 +3460,13 @@
         <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>221</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>29</v>
@@ -3527,12 +3527,12 @@
         <v>45750</v>
       </c>
       <c r="AB10" s="71" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>50</v>
@@ -3544,13 +3544,13 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F11" s="38" t="s">
         <v>220</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>29</v>
@@ -3609,12 +3609,12 @@
         <v>45750</v>
       </c>
       <c r="AB11" s="71" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>50</v>
@@ -3626,13 +3626,13 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>181</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>29</v>
@@ -3693,12 +3693,12 @@
         <v>45750</v>
       </c>
       <c r="AB12" s="71" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>78</v>
@@ -3710,13 +3710,13 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>182</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>29</v>
@@ -3777,12 +3777,12 @@
         <v>45750</v>
       </c>
       <c r="AB13" s="71" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>78</v>
@@ -3794,13 +3794,13 @@
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>183</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>29</v>
@@ -3861,12 +3861,12 @@
         <v>45750</v>
       </c>
       <c r="AB14" s="71" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>78</v>
@@ -3878,13 +3878,13 @@
         <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>184</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>29</v>
@@ -3945,12 +3945,12 @@
         <v>45750</v>
       </c>
       <c r="AB15" s="71" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>27</v>
@@ -3962,13 +3962,13 @@
         <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>185</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>29</v>
@@ -4029,12 +4029,12 @@
         <v>45750</v>
       </c>
       <c r="AB16" s="71" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>27</v>
@@ -4046,13 +4046,13 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>186</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>29</v>
@@ -4113,12 +4113,12 @@
         <v>45750</v>
       </c>
       <c r="AB17" s="71" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>27</v>
@@ -4130,13 +4130,13 @@
         <v>17</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>187</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H18" s="5" t="s">
         <v>29</v>
@@ -4197,12 +4197,12 @@
         <v>45750</v>
       </c>
       <c r="AB18" s="71" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>99</v>
@@ -4214,13 +4214,13 @@
         <v>18</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>189</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>40</v>
@@ -4281,12 +4281,12 @@
         <v>45750</v>
       </c>
       <c r="AB19" s="73" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>99</v>
@@ -4298,13 +4298,13 @@
         <v>19</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>190</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H20" s="5" t="s">
         <v>29</v>
@@ -4365,12 +4365,12 @@
         <v>45750</v>
       </c>
       <c r="AB20" s="73" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>99</v>
@@ -4382,13 +4382,13 @@
         <v>20</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>191</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H21" s="5" t="s">
         <v>29</v>
@@ -4449,12 +4449,12 @@
         <v>45750</v>
       </c>
       <c r="AB21" s="73" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>99</v>
@@ -4466,13 +4466,13 @@
         <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>192</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>29</v>
@@ -4533,12 +4533,12 @@
         <v>45750</v>
       </c>
       <c r="AB22" s="73" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>99</v>
@@ -4550,13 +4550,13 @@
         <v>22</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>193</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H23" s="5" t="s">
         <v>29</v>
@@ -4613,18 +4613,18 @@
         <v>1</v>
       </c>
       <c r="Z23" s="76" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AA23" s="12">
         <v>45750</v>
       </c>
       <c r="AB23" s="37" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>99</v>
@@ -4636,13 +4636,13 @@
         <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>207</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H24" s="5" t="s">
         <v>29</v>
@@ -4703,12 +4703,12 @@
         <v>45750</v>
       </c>
       <c r="AB24" s="37" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>99</v>
@@ -4720,13 +4720,13 @@
         <v>24</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>202</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H25" s="5" t="s">
         <v>29</v>
@@ -4774,7 +4774,7 @@
         <v>91</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="X25" s="10" t="b">
         <v>1</v>
@@ -4787,12 +4787,12 @@
         <v>45750</v>
       </c>
       <c r="AB25" s="37" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="12" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>99</v>
@@ -4804,13 +4804,13 @@
         <v>25</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>194</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H26" s="5" t="s">
         <v>29</v>
@@ -4858,7 +4858,7 @@
         <v>91</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="X26" s="10" t="b">
         <v>1</v>
@@ -4871,12 +4871,12 @@
         <v>45750</v>
       </c>
       <c r="AB26" s="37" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="12" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>99</v>
@@ -4888,13 +4888,13 @@
         <v>26</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>203</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H27" s="5" t="s">
         <v>29</v>
@@ -4942,7 +4942,7 @@
         <v>91</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="X27" s="10" t="b">
         <v>1</v>
@@ -4955,12 +4955,12 @@
         <v>45750</v>
       </c>
       <c r="AB27" s="37" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="12" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>99</v>
@@ -4972,13 +4972,13 @@
         <v>27</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>204</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H28" s="5" t="s">
         <v>29</v>
@@ -5039,12 +5039,12 @@
         <v>45750</v>
       </c>
       <c r="AB28" s="37" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="12" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>99</v>
@@ -5056,13 +5056,13 @@
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>205</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H29" s="5" t="s">
         <v>29</v>
@@ -5110,7 +5110,7 @@
         <v>91</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="X29" s="10" t="b">
         <v>1</v>
@@ -5123,12 +5123,12 @@
         <v>45750</v>
       </c>
       <c r="AB29" s="37" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="12" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>99</v>
@@ -5140,13 +5140,13 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>206</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H30" s="5" t="s">
         <v>29</v>
@@ -5194,7 +5194,7 @@
         <v>91</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="X30" s="10" t="b">
         <v>1</v>
@@ -5207,12 +5207,12 @@
         <v>45750</v>
       </c>
       <c r="AB30" s="37" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>99</v>
@@ -5224,13 +5224,13 @@
         <v>30</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>208</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H31" s="5" t="s">
         <v>29</v>
@@ -5278,7 +5278,7 @@
         <v>91</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="X31" s="10" t="b">
         <v>1</v>
@@ -5291,12 +5291,12 @@
         <v>45750</v>
       </c>
       <c r="AB31" s="37" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="12" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>99</v>
@@ -5308,13 +5308,13 @@
         <v>31</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>209</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="H32" s="5" t="s">
         <v>29</v>
@@ -5362,7 +5362,7 @@
         <v>91</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="X32" s="10" t="b">
         <v>1</v>
@@ -5375,7 +5375,7 @@
         <v>45750</v>
       </c>
       <c r="AB32" s="37" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
     </row>
     <row r="33" spans="4:14" ht="12" customHeight="1">
@@ -10329,7 +10329,7 @@
         <v>171</v>
       </c>
       <c r="O1" s="63" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="P1" s="22"/>
       <c r="Q1" s="22"/>
@@ -10375,7 +10375,7 @@
       </c>
       <c r="N2" s="35"/>
       <c r="O2" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q2"/>
     </row>
@@ -10419,7 +10419,7 @@
       </c>
       <c r="N3" s="35"/>
       <c r="O3" s="57" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="Q3"/>
     </row>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="N4" s="35"/>
       <c r="O4" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q4"/>
     </row>
@@ -10507,7 +10507,7 @@
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q5"/>
     </row>
@@ -10549,7 +10549,7 @@
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q6"/>
     </row>
@@ -10591,7 +10591,7 @@
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q7"/>
     </row>
@@ -10633,7 +10633,7 @@
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="57" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="Q8"/>
     </row>
@@ -10651,10 +10651,10 @@
         <v>33</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="3" t="s">
@@ -10670,7 +10670,7 @@
         <v>149</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="M9" s="3" t="b">
         <v>1</v>
@@ -10692,10 +10692,10 @@
         <v>33</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="3" t="s">
@@ -10711,7 +10711,7 @@
         <v>149</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="M10" s="3" t="b">
         <v>1</v>
@@ -10752,7 +10752,7 @@
         <v>149</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="M11" s="3" t="b">
         <v>1</v>
@@ -11139,7 +11139,7 @@
         <v>149</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="M20" s="3" t="b">
         <v>1</v>
@@ -11189,7 +11189,7 @@
       </c>
       <c r="N21" s="35"/>
       <c r="O21" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q21"/>
     </row>
@@ -11233,7 +11233,7 @@
       </c>
       <c r="N22" s="35"/>
       <c r="O22" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q22"/>
     </row>
@@ -11483,7 +11483,7 @@
       </c>
       <c r="N28" s="35"/>
       <c r="O28" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q28"/>
     </row>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="N29" s="35"/>
       <c r="O29" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q29"/>
     </row>
@@ -11776,7 +11776,7 @@
       </c>
       <c r="N35" s="35"/>
       <c r="O35" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q35"/>
     </row>
@@ -11820,7 +11820,7 @@
       </c>
       <c r="N36" s="35"/>
       <c r="O36" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q36"/>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="N42" s="35"/>
       <c r="O42" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q42"/>
     </row>
@@ -12113,7 +12113,7 @@
       </c>
       <c r="N43" s="35"/>
       <c r="O43" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q43"/>
     </row>
@@ -12362,7 +12362,7 @@
       </c>
       <c r="N49" s="35"/>
       <c r="O49" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q49"/>
     </row>
@@ -12406,7 +12406,7 @@
       </c>
       <c r="N50" s="35"/>
       <c r="O50" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q50"/>
     </row>
@@ -12655,7 +12655,7 @@
       </c>
       <c r="N56" s="35"/>
       <c r="O56" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q56"/>
     </row>
@@ -12699,7 +12699,7 @@
       </c>
       <c r="N57" s="35"/>
       <c r="O57" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q57"/>
     </row>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="N63" s="35"/>
       <c r="O63" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q63"/>
     </row>
@@ -12992,7 +12992,7 @@
       </c>
       <c r="N64" s="35"/>
       <c r="O64" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q64"/>
     </row>
@@ -13241,7 +13241,7 @@
       </c>
       <c r="N70" s="35"/>
       <c r="O70" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q70"/>
     </row>
@@ -13285,7 +13285,7 @@
       </c>
       <c r="N71" s="35"/>
       <c r="O71" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q71"/>
     </row>
@@ -13534,7 +13534,7 @@
       </c>
       <c r="N77" s="35"/>
       <c r="O77" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q77"/>
     </row>
@@ -13578,7 +13578,7 @@
       </c>
       <c r="N78" s="35"/>
       <c r="O78" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q78"/>
     </row>
@@ -13827,7 +13827,7 @@
       </c>
       <c r="N84" s="35"/>
       <c r="O84" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q84"/>
     </row>
@@ -13871,7 +13871,7 @@
       </c>
       <c r="N85" s="35"/>
       <c r="O85" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q85"/>
     </row>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="N91" s="35"/>
       <c r="O91" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q91"/>
     </row>
@@ -14164,7 +14164,7 @@
       </c>
       <c r="N92" s="35"/>
       <c r="O92" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q92"/>
     </row>
@@ -14413,7 +14413,7 @@
       </c>
       <c r="N98" s="35"/>
       <c r="O98" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q98"/>
     </row>
@@ -14457,7 +14457,7 @@
       </c>
       <c r="N99" s="35"/>
       <c r="O99" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q99"/>
     </row>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="N105" s="35"/>
       <c r="O105" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q105"/>
     </row>
@@ -14750,7 +14750,7 @@
       </c>
       <c r="N106" s="35"/>
       <c r="O106" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q106"/>
     </row>
@@ -14999,7 +14999,7 @@
       </c>
       <c r="N112" s="35"/>
       <c r="O112" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q112"/>
     </row>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="N113" s="35"/>
       <c r="O113" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q113"/>
     </row>
@@ -15292,7 +15292,7 @@
       </c>
       <c r="N119" s="35"/>
       <c r="O119" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q119"/>
     </row>
@@ -15336,7 +15336,7 @@
       </c>
       <c r="N120" s="35"/>
       <c r="O120" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q120"/>
     </row>
@@ -15585,7 +15585,7 @@
       </c>
       <c r="N126" s="35"/>
       <c r="O126" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q126"/>
     </row>
@@ -15629,7 +15629,7 @@
       </c>
       <c r="N127" s="35"/>
       <c r="O127" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q127"/>
     </row>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="N133" s="35"/>
       <c r="O133" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q133"/>
     </row>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="N134" s="35"/>
       <c r="O134" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q134"/>
     </row>
@@ -16171,7 +16171,7 @@
       </c>
       <c r="N140" s="35"/>
       <c r="O140" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q140"/>
     </row>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="N141" s="35"/>
       <c r="O141" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q141"/>
     </row>
@@ -16464,7 +16464,7 @@
       </c>
       <c r="N147" s="35"/>
       <c r="O147" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q147"/>
     </row>
@@ -16508,7 +16508,7 @@
       </c>
       <c r="N148" s="35"/>
       <c r="O148" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q148"/>
     </row>
@@ -16757,7 +16757,7 @@
       </c>
       <c r="N154" s="35"/>
       <c r="O154" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q154"/>
     </row>
@@ -16801,7 +16801,7 @@
       </c>
       <c r="N155" s="35"/>
       <c r="O155" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q155"/>
     </row>
@@ -17050,7 +17050,7 @@
       </c>
       <c r="N161" s="35"/>
       <c r="O161" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q161"/>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="N162" s="35"/>
       <c r="O162" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q162"/>
     </row>
@@ -17343,7 +17343,7 @@
       </c>
       <c r="N168" s="35"/>
       <c r="O168" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="Q168"/>
     </row>
@@ -17387,7 +17387,7 @@
       </c>
       <c r="N169" s="35"/>
       <c r="O169" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="Q169"/>
     </row>
@@ -17636,7 +17636,7 @@
       </c>
       <c r="N175" s="7"/>
       <c r="O175" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="176" spans="1:17" ht="12" customHeight="1">
@@ -17679,7 +17679,7 @@
       </c>
       <c r="N176" s="7"/>
       <c r="O176" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="177" spans="1:15" ht="12" customHeight="1">
@@ -17927,7 +17927,7 @@
       </c>
       <c r="N182" s="7"/>
       <c r="O182" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="183" spans="1:15" ht="12" customHeight="1">
@@ -17970,7 +17970,7 @@
       </c>
       <c r="N183" s="7"/>
       <c r="O183" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="184" spans="1:15" ht="12" customHeight="1">
@@ -18218,7 +18218,7 @@
       </c>
       <c r="N189" s="7"/>
       <c r="O189" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="190" spans="1:15" ht="12" customHeight="1">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="N190" s="7"/>
       <c r="O190" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="191" spans="1:15" ht="12" customHeight="1">
@@ -18509,7 +18509,7 @@
       </c>
       <c r="N196" s="7"/>
       <c r="O196" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="197" spans="1:15" ht="12" customHeight="1">
@@ -18552,7 +18552,7 @@
       </c>
       <c r="N197" s="7"/>
       <c r="O197" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="198" spans="1:15" ht="12" customHeight="1">
@@ -18800,7 +18800,7 @@
       </c>
       <c r="N203" s="7"/>
       <c r="O203" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="204" spans="1:15" ht="12" customHeight="1">
@@ -18843,7 +18843,7 @@
       </c>
       <c r="N204" s="7"/>
       <c r="O204" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="12" customHeight="1">
@@ -19091,7 +19091,7 @@
       </c>
       <c r="N210" s="7"/>
       <c r="O210" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="211" spans="1:15" ht="12" customHeight="1">
@@ -19134,7 +19134,7 @@
       </c>
       <c r="N211" s="7"/>
       <c r="O211" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="212" spans="1:15" ht="12" customHeight="1">
@@ -19379,7 +19379,7 @@
       </c>
       <c r="N217" s="7"/>
       <c r="O217" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="218" spans="1:15" ht="12" customHeight="1">
@@ -19422,7 +19422,7 @@
       </c>
       <c r="N218" s="7"/>
       <c r="O218" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="219" spans="1:15" ht="12" customHeight="1">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="N224" s="7"/>
       <c r="O224" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="225" spans="1:15" ht="12" customHeight="1">
@@ -19708,7 +19708,7 @@
       </c>
       <c r="N225" s="7"/>
       <c r="O225" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="226" spans="1:15" ht="12" customHeight="1">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="N231" s="7"/>
       <c r="O231" s="57" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="232" spans="1:15" ht="12" customHeight="1">
@@ -19994,7 +19994,7 @@
       </c>
       <c r="N232" s="7"/>
       <c r="O232" s="57" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="233" spans="1:15" ht="12" customHeight="1">
@@ -23034,16 +23034,16 @@
         <v>223</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="F2" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>151</v>
@@ -23055,10 +23055,10 @@
         <v>173</v>
       </c>
       <c r="J2" s="45" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="K2" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23069,16 +23069,16 @@
         <v>224</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="F3" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G3" s="40" t="s">
         <v>154</v>
@@ -23090,10 +23090,10 @@
         <v>31</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="K3" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23104,16 +23104,16 @@
         <v>225</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F4" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G4" s="43" t="s">
         <v>151</v>
@@ -23125,10 +23125,10 @@
         <v>31</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K4" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23139,16 +23139,16 @@
         <v>226</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G5" s="49" t="s">
         <v>151</v>
@@ -23163,7 +23163,7 @@
         <v>44</v>
       </c>
       <c r="K5" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23174,16 +23174,16 @@
         <v>227</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E6" s="41" t="s">
+        <v>363</v>
+      </c>
+      <c r="F6" s="77" t="s">
         <v>366</v>
-      </c>
-      <c r="F6" s="77" t="s">
-        <v>369</v>
       </c>
       <c r="G6" s="43" t="s">
         <v>151</v>
@@ -23195,10 +23195,10 @@
         <v>31</v>
       </c>
       <c r="J6" s="45" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K6" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23209,16 +23209,16 @@
         <v>228</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G7" s="49" t="s">
         <v>151</v>
@@ -23233,7 +23233,7 @@
         <v>44</v>
       </c>
       <c r="K7" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23244,16 +23244,16 @@
         <v>229</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G8" s="41" t="s">
         <v>154</v>
@@ -23265,10 +23265,10 @@
         <v>31</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="K8" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23279,14 +23279,14 @@
         <v>230</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D9" s="47"/>
       <c r="E9" s="40" t="s">
         <v>156</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G9" s="49" t="s">
         <v>151</v>
@@ -23298,10 +23298,10 @@
         <v>31</v>
       </c>
       <c r="J9" s="51" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="K9" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23312,14 +23312,14 @@
         <v>233</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D10" s="44"/>
       <c r="E10" s="41" t="s">
         <v>158</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G10" s="43" t="s">
         <v>151</v>
@@ -23331,10 +23331,10 @@
         <v>31</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K10" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23345,14 +23345,14 @@
         <v>234</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D11" s="47"/>
       <c r="E11" s="40" t="s">
         <v>160</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G11" s="49" t="s">
         <v>151</v>
@@ -23367,7 +23367,7 @@
         <v>161</v>
       </c>
       <c r="K11" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23378,14 +23378,14 @@
         <v>235</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D12" s="44"/>
       <c r="E12" s="50" t="s">
         <v>150</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G12" s="43" t="s">
         <v>151</v>
@@ -23400,7 +23400,7 @@
         <v>152</v>
       </c>
       <c r="K12" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23411,14 +23411,14 @@
         <v>236</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="50" t="s">
         <v>153</v>
       </c>
       <c r="F13" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G13" s="40" t="s">
         <v>154</v>
@@ -23433,7 +23433,7 @@
         <v>155</v>
       </c>
       <c r="K13" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23444,14 +23444,14 @@
         <v>237</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D14" s="44"/>
       <c r="E14" s="50" t="s">
         <v>156</v>
       </c>
       <c r="F14" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>151</v>
@@ -23466,7 +23466,7 @@
         <v>157</v>
       </c>
       <c r="K14" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23477,14 +23477,14 @@
         <v>238</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D15" s="47"/>
       <c r="E15" s="50" t="s">
         <v>158</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G15" s="49" t="s">
         <v>151</v>
@@ -23496,10 +23496,10 @@
         <v>31</v>
       </c>
       <c r="J15" s="45" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="K15" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23510,14 +23510,14 @@
         <v>239</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="50" t="s">
         <v>160</v>
       </c>
       <c r="F16" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G16" s="43" t="s">
         <v>151</v>
@@ -23529,10 +23529,10 @@
         <v>31</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K16" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23543,7 +23543,7 @@
         <v>240</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>162</v>
@@ -23552,7 +23552,7 @@
         <v>150</v>
       </c>
       <c r="F17" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>151</v>
@@ -23564,10 +23564,10 @@
         <v>31</v>
       </c>
       <c r="J17" s="45" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="K17" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23578,7 +23578,7 @@
         <v>241</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D18" s="44" t="s">
         <v>163</v>
@@ -23587,7 +23587,7 @@
         <v>153</v>
       </c>
       <c r="F18" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G18" s="41" t="s">
         <v>154</v>
@@ -23602,7 +23602,7 @@
         <v>44</v>
       </c>
       <c r="K18" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23613,14 +23613,14 @@
         <v>242</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D19" s="47"/>
       <c r="E19" s="50" t="s">
         <v>156</v>
       </c>
       <c r="F19" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G19" s="49" t="s">
         <v>151</v>
@@ -23632,10 +23632,10 @@
         <v>31</v>
       </c>
       <c r="J19" s="45" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="K19" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23646,14 +23646,14 @@
         <v>243</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D20" s="44"/>
       <c r="E20" s="55" t="s">
         <v>158</v>
       </c>
       <c r="F20" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G20" s="43" t="s">
         <v>151</v>
@@ -23665,10 +23665,10 @@
         <v>31</v>
       </c>
       <c r="J20" s="45" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="K20" s="57" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23679,7 +23679,7 @@
         <v>244</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D21" s="47" t="s">
         <v>159</v>
@@ -23688,7 +23688,7 @@
         <v>160</v>
       </c>
       <c r="F21" s="77" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="G21" s="49" t="s">
         <v>151</v>
@@ -23700,7 +23700,7 @@
         <v>31</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="K21" s="57" t="s">
         <v>246</v>
@@ -23781,7 +23781,7 @@
         <v>125</v>
       </c>
       <c r="C1" s="61" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D1" s="61" t="s">
         <v>134</v>
@@ -23790,7 +23790,7 @@
         <v>251</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="G1" s="28" t="s">
         <v>252</v>
@@ -23802,22 +23802,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="67" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>253</v>
+        <v>375</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F2" s="70" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G2" s="70" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H2" s="64"/>
       <c r="I2" s="65"/>
@@ -23827,22 +23827,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>258</v>
+        <v>376</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F3" s="70" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G3" s="70" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="H3" s="29"/>
     </row>
@@ -23851,22 +23851,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>259</v>
+        <v>377</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="F4" s="70" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G4" s="70" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="12" customHeight="1"/>
@@ -24876,13 +24876,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="12" customHeight="1">
       <c r="A1" s="29" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D1" s="29" t="s">
         <v>135</v>
@@ -24893,13 +24893,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1">

--- a/360MasterData_CH.xlsx
+++ b/360MasterData_CH.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAB0D797-2C97-4FB2-871B-8EC773BF524F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F4BBC1-B8F0-4E88-8E8F-402AF7671A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="373">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="372">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -987,9 +987,6 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/HS-HYP-01.svg</t>
-  </si>
-  <si>
-    <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/WelcomeVC.mp3</t>
   </si>
   <si>
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/HS1-4.mp3</t>
@@ -2766,7 +2763,7 @@
     </row>
     <row r="2" spans="1:28" ht="18.3" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -2778,7 +2775,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F2" s="38" t="s">
         <v>180</v>
@@ -2787,13 +2784,13 @@
         <v>267</v>
       </c>
       <c r="H2" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I2" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J2" s="62" t="s">
-        <v>298</v>
+        <v>361</v>
       </c>
       <c r="K2" s="62" t="s">
         <v>165</v>
@@ -2832,7 +2829,7 @@
         <v>290</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X2" s="10" t="b">
         <v>1</v>
@@ -2841,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="Z2" s="68" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AA2" s="12">
         <v>45750</v>
@@ -2852,7 +2849,7 @@
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -2864,7 +2861,7 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F3" s="38" t="s">
         <v>171</v>
@@ -2873,7 +2870,7 @@
         <v>267</v>
       </c>
       <c r="H3" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I3" s="13" t="b">
         <v>0</v>
@@ -2927,7 +2924,7 @@
         <v>1</v>
       </c>
       <c r="Z3" s="76" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="AA3" s="12">
         <v>45750</v>
@@ -2938,7 +2935,7 @@
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -2950,7 +2947,7 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F4" s="38" t="s">
         <v>170</v>
@@ -2959,7 +2956,7 @@
         <v>267</v>
       </c>
       <c r="H4" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I4" s="3" t="b">
         <v>1</v>
@@ -3019,7 +3016,7 @@
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -3031,7 +3028,7 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F5" s="38" t="s">
         <v>168</v>
@@ -3040,7 +3037,7 @@
         <v>267</v>
       </c>
       <c r="H5" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I5" s="3" t="b">
         <v>1</v>
@@ -3101,7 +3098,7 @@
     </row>
     <row r="6" spans="1:28" ht="20.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
@@ -3113,7 +3110,7 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F6" s="38" t="s">
         <v>169</v>
@@ -3122,7 +3119,7 @@
         <v>267</v>
       </c>
       <c r="H6" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I6" s="3" t="b">
         <v>1</v>
@@ -3183,7 +3180,7 @@
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
@@ -3195,7 +3192,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F7" s="38" t="s">
         <v>172</v>
@@ -3204,13 +3201,13 @@
         <v>267</v>
       </c>
       <c r="H7" s="62" t="s">
+        <v>369</v>
+      </c>
+      <c r="I7" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" s="16" t="s">
         <v>370</v>
-      </c>
-      <c r="I7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J7" s="16" t="s">
-        <v>371</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>50</v>
@@ -3265,7 +3262,7 @@
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>48</v>
@@ -3277,7 +3274,7 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F8" s="38" t="s">
         <v>193</v>
@@ -3286,13 +3283,13 @@
         <v>267</v>
       </c>
       <c r="H8" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I8" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>30</v>
@@ -3331,7 +3328,7 @@
         <v>33</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="X8" s="15" t="b">
         <v>0</v>
@@ -3349,7 +3346,7 @@
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>48</v>
@@ -3361,7 +3358,7 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F9" s="38" t="s">
         <v>167</v>
@@ -3370,13 +3367,13 @@
         <v>267</v>
       </c>
       <c r="H9" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I9" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>57</v>
@@ -3433,7 +3430,7 @@
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>48</v>
@@ -3445,7 +3442,7 @@
         <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F10" s="38" t="s">
         <v>213</v>
@@ -3454,7 +3451,7 @@
         <v>267</v>
       </c>
       <c r="H10" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I10" s="3" t="b">
         <v>1</v>
@@ -3517,7 +3514,7 @@
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>48</v>
@@ -3529,7 +3526,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F11" s="38" t="s">
         <v>212</v>
@@ -3538,7 +3535,7 @@
         <v>267</v>
       </c>
       <c r="H11" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I11" s="3" t="b">
         <v>1</v>
@@ -3599,7 +3596,7 @@
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>48</v>
@@ -3611,7 +3608,7 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F12" s="38" t="s">
         <v>173</v>
@@ -3620,7 +3617,7 @@
         <v>267</v>
       </c>
       <c r="H12" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I12" s="3" t="b">
         <v>1</v>
@@ -3683,7 +3680,7 @@
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>72</v>
@@ -3695,7 +3692,7 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F13" s="38" t="s">
         <v>174</v>
@@ -3704,7 +3701,7 @@
         <v>267</v>
       </c>
       <c r="H13" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I13" s="3" t="b">
         <v>1</v>
@@ -3767,7 +3764,7 @@
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>72</v>
@@ -3779,7 +3776,7 @@
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F14" s="38" t="s">
         <v>175</v>
@@ -3788,7 +3785,7 @@
         <v>267</v>
       </c>
       <c r="H14" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I14" s="3" t="b">
         <v>1</v>
@@ -3851,7 +3848,7 @@
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>72</v>
@@ -3863,7 +3860,7 @@
         <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F15" s="38" t="s">
         <v>176</v>
@@ -3872,7 +3869,7 @@
         <v>267</v>
       </c>
       <c r="H15" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I15" s="3" t="b">
         <v>1</v>
@@ -3935,7 +3932,7 @@
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>27</v>
@@ -3947,7 +3944,7 @@
         <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F16" s="38" t="s">
         <v>177</v>
@@ -3956,7 +3953,7 @@
         <v>267</v>
       </c>
       <c r="H16" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I16" s="13" t="b">
         <v>0</v>
@@ -4019,7 +4016,7 @@
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>27</v>
@@ -4031,7 +4028,7 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F17" s="38" t="s">
         <v>178</v>
@@ -4040,7 +4037,7 @@
         <v>267</v>
       </c>
       <c r="H17" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I17" s="3" t="b">
         <v>1</v>
@@ -4103,7 +4100,7 @@
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>27</v>
@@ -4115,7 +4112,7 @@
         <v>17</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F18" s="38" t="s">
         <v>179</v>
@@ -4124,7 +4121,7 @@
         <v>267</v>
       </c>
       <c r="H18" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I18" s="3" t="b">
         <v>1</v>
@@ -4187,7 +4184,7 @@
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>93</v>
@@ -4199,7 +4196,7 @@
         <v>18</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F19" s="38" t="s">
         <v>181</v>
@@ -4208,13 +4205,13 @@
         <v>267</v>
       </c>
       <c r="H19" s="62" t="s">
+        <v>369</v>
+      </c>
+      <c r="I19" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="J19" s="16" t="s">
         <v>370</v>
-      </c>
-      <c r="I19" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="J19" s="16" t="s">
-        <v>371</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>95</v>
@@ -4271,7 +4268,7 @@
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>93</v>
@@ -4283,7 +4280,7 @@
         <v>19</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F20" s="38" t="s">
         <v>182</v>
@@ -4292,13 +4289,13 @@
         <v>267</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I20" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>30</v>
@@ -4355,7 +4352,7 @@
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>93</v>
@@ -4367,7 +4364,7 @@
         <v>20</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F21" s="38" t="s">
         <v>183</v>
@@ -4376,7 +4373,7 @@
         <v>267</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I21" s="3" t="b">
         <v>1</v>
@@ -4439,7 +4436,7 @@
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>93</v>
@@ -4451,7 +4448,7 @@
         <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F22" s="38" t="s">
         <v>184</v>
@@ -4460,7 +4457,7 @@
         <v>267</v>
       </c>
       <c r="H22" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I22" s="3" t="b">
         <v>1</v>
@@ -4523,7 +4520,7 @@
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>93</v>
@@ -4535,7 +4532,7 @@
         <v>22</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F23" s="38" t="s">
         <v>185</v>
@@ -4544,7 +4541,7 @@
         <v>267</v>
       </c>
       <c r="H23" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I23" s="3" t="b">
         <v>1</v>
@@ -4609,7 +4606,7 @@
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>93</v>
@@ -4621,7 +4618,7 @@
         <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F24" s="38" t="s">
         <v>199</v>
@@ -4630,7 +4627,7 @@
         <v>267</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I24" s="3" t="b">
         <v>1</v>
@@ -4693,7 +4690,7 @@
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>93</v>
@@ -4705,7 +4702,7 @@
         <v>24</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F25" s="38" t="s">
         <v>194</v>
@@ -4714,7 +4711,7 @@
         <v>267</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I25" s="3" t="b">
         <v>1</v>
@@ -4777,7 +4774,7 @@
     </row>
     <row r="26" spans="1:28" ht="12" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>93</v>
@@ -4789,7 +4786,7 @@
         <v>25</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F26" s="38" t="s">
         <v>186</v>
@@ -4798,7 +4795,7 @@
         <v>267</v>
       </c>
       <c r="H26" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I26" s="3" t="b">
         <v>1</v>
@@ -4861,7 +4858,7 @@
     </row>
     <row r="27" spans="1:28" ht="12" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>93</v>
@@ -4873,7 +4870,7 @@
         <v>26</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F27" s="38" t="s">
         <v>195</v>
@@ -4882,7 +4879,7 @@
         <v>267</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I27" s="3" t="b">
         <v>1</v>
@@ -4945,7 +4942,7 @@
     </row>
     <row r="28" spans="1:28" ht="12" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>93</v>
@@ -4957,7 +4954,7 @@
         <v>27</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F28" s="38" t="s">
         <v>196</v>
@@ -4966,7 +4963,7 @@
         <v>267</v>
       </c>
       <c r="H28" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I28" s="3" t="b">
         <v>1</v>
@@ -5029,7 +5026,7 @@
     </row>
     <row r="29" spans="1:28" ht="12" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>93</v>
@@ -5041,7 +5038,7 @@
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="38" t="s">
         <v>197</v>
@@ -5050,7 +5047,7 @@
         <v>267</v>
       </c>
       <c r="H29" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I29" s="3" t="b">
         <v>1</v>
@@ -5113,7 +5110,7 @@
     </row>
     <row r="30" spans="1:28" ht="12" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>93</v>
@@ -5125,7 +5122,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F30" s="38" t="s">
         <v>198</v>
@@ -5134,7 +5131,7 @@
         <v>267</v>
       </c>
       <c r="H30" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I30" s="3" t="b">
         <v>1</v>
@@ -5197,7 +5194,7 @@
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>93</v>
@@ -5209,7 +5206,7 @@
         <v>30</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F31" s="38" t="s">
         <v>200</v>
@@ -5218,7 +5215,7 @@
         <v>267</v>
       </c>
       <c r="H31" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I31" s="3" t="b">
         <v>1</v>
@@ -5281,7 +5278,7 @@
     </row>
     <row r="32" spans="1:28" ht="12" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>93</v>
@@ -5293,7 +5290,7 @@
         <v>31</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F32" s="38" t="s">
         <v>201</v>
@@ -5302,7 +5299,7 @@
         <v>267</v>
       </c>
       <c r="H32" s="62" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I32" s="3" t="b">
         <v>1</v>
@@ -10401,7 +10398,7 @@
       </c>
       <c r="N3" s="35"/>
       <c r="O3" s="57" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="Q3"/>
     </row>
@@ -23019,13 +23016,13 @@
         <v>292</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="F2" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>143</v>
@@ -23037,7 +23034,7 @@
         <v>165</v>
       </c>
       <c r="J2" s="45" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="K2" s="57" t="s">
         <v>268</v>
@@ -23054,13 +23051,13 @@
         <v>293</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F3" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G3" s="40" t="s">
         <v>146</v>
@@ -23072,7 +23069,7 @@
         <v>30</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K3" s="57" t="s">
         <v>268</v>
@@ -23089,13 +23086,13 @@
         <v>295</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F4" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G4" s="43" t="s">
         <v>143</v>
@@ -23107,7 +23104,7 @@
         <v>30</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K4" s="57" t="s">
         <v>268</v>
@@ -23124,13 +23121,13 @@
         <v>296</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G5" s="49" t="s">
         <v>143</v>
@@ -23159,13 +23156,13 @@
         <v>296</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E6" s="41" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F6" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G6" s="43" t="s">
         <v>143</v>
@@ -23177,7 +23174,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="45" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K6" s="57" t="s">
         <v>268</v>
@@ -23194,13 +23191,13 @@
         <v>296</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G7" s="49" t="s">
         <v>143</v>
@@ -23229,13 +23226,13 @@
         <v>296</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E8" s="41" t="s">
+        <v>356</v>
+      </c>
+      <c r="F8" s="77" t="s">
         <v>357</v>
-      </c>
-      <c r="F8" s="77" t="s">
-        <v>358</v>
       </c>
       <c r="G8" s="41" t="s">
         <v>146</v>
@@ -23247,7 +23244,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="K8" s="57" t="s">
         <v>268</v>
@@ -23268,7 +23265,7 @@
         <v>148</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G9" s="49" t="s">
         <v>143</v>
@@ -23280,7 +23277,7 @@
         <v>30</v>
       </c>
       <c r="J9" s="51" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K9" s="57" t="s">
         <v>268</v>
@@ -23301,7 +23298,7 @@
         <v>150</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G10" s="43" t="s">
         <v>143</v>
@@ -23313,7 +23310,7 @@
         <v>30</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K10" s="57" t="s">
         <v>268</v>
@@ -23334,7 +23331,7 @@
         <v>152</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G11" s="49" t="s">
         <v>143</v>
@@ -23367,7 +23364,7 @@
         <v>142</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G12" s="43" t="s">
         <v>143</v>
@@ -23400,7 +23397,7 @@
         <v>145</v>
       </c>
       <c r="F13" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G13" s="40" t="s">
         <v>146</v>
@@ -23433,7 +23430,7 @@
         <v>148</v>
       </c>
       <c r="F14" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>143</v>
@@ -23466,7 +23463,7 @@
         <v>150</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G15" s="49" t="s">
         <v>143</v>
@@ -23478,7 +23475,7 @@
         <v>30</v>
       </c>
       <c r="J15" s="45" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K15" s="57" t="s">
         <v>268</v>
@@ -23499,7 +23496,7 @@
         <v>152</v>
       </c>
       <c r="F16" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G16" s="43" t="s">
         <v>143</v>
@@ -23511,7 +23508,7 @@
         <v>30</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K16" s="57" t="s">
         <v>268</v>
@@ -23534,7 +23531,7 @@
         <v>142</v>
       </c>
       <c r="F17" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>143</v>
@@ -23546,7 +23543,7 @@
         <v>30</v>
       </c>
       <c r="J17" s="45" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="K17" s="57" t="s">
         <v>268</v>
@@ -23569,7 +23566,7 @@
         <v>145</v>
       </c>
       <c r="F18" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G18" s="41" t="s">
         <v>146</v>
@@ -23602,7 +23599,7 @@
         <v>148</v>
       </c>
       <c r="F19" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G19" s="49" t="s">
         <v>143</v>
@@ -23614,7 +23611,7 @@
         <v>30</v>
       </c>
       <c r="J19" s="45" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="K19" s="57" t="s">
         <v>268</v>
@@ -23635,7 +23632,7 @@
         <v>150</v>
       </c>
       <c r="F20" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G20" s="43" t="s">
         <v>143</v>
@@ -23647,7 +23644,7 @@
         <v>30</v>
       </c>
       <c r="J20" s="45" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="K20" s="57" t="s">
         <v>268</v>
@@ -23670,7 +23667,7 @@
         <v>152</v>
       </c>
       <c r="F21" s="77" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="G21" s="49" t="s">
         <v>143</v>
@@ -23682,7 +23679,7 @@
         <v>30</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="K21" s="57" t="s">
         <v>238</v>
@@ -23790,13 +23787,13 @@
         <v>260</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F2" s="70" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G2" s="70" t="s">
         <v>252</v>
@@ -23815,16 +23812,16 @@
         <v>260</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F3" s="70" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G3" s="70" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H3" s="29"/>
     </row>
@@ -23839,13 +23836,13 @@
         <v>260</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F4" s="70" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G4" s="70" t="s">
         <v>252</v>
@@ -24858,13 +24855,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="12" customHeight="1">
       <c r="A1" s="29" t="s">
+        <v>302</v>
+      </c>
+      <c r="B1" s="29" t="s">
         <v>303</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="C1" s="29" t="s">
         <v>304</v>
-      </c>
-      <c r="C1" s="29" t="s">
-        <v>305</v>
       </c>
       <c r="D1" s="29" t="s">
         <v>127</v>
@@ -24875,13 +24872,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
+        <v>364</v>
+      </c>
+      <c r="C2" s="57" t="s">
+        <v>361</v>
+      </c>
+      <c r="D2" s="29" t="s">
         <v>365</v>
-      </c>
-      <c r="C2" s="57" t="s">
-        <v>362</v>
-      </c>
-      <c r="D2" s="29" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1">

--- a/360MasterData_CH.xlsx
+++ b/360MasterData_CH.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RiyasMoosa\Downloads\Codes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47F4BBC1-B8F0-4E88-8E8F-402AF7671A49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE27CF2-D9D4-449F-B30A-F46D639EA313}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1. Scenes Sheet" sheetId="1" r:id="rId1"/>
@@ -65,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2653" uniqueCount="370">
   <si>
     <t>FloorGroupName</t>
   </si>
@@ -520,9 +520,6 @@
     <t>https://raw.githubusercontent.com/Rmoosa2014/vr-tour/main/SRcurrency.svg</t>
   </si>
   <si>
-    <t>"Hey, Check this our new premium collections of the Safas"</t>
-  </si>
-  <si>
     <t>Premium Tables</t>
   </si>
   <si>
@@ -535,9 +532,6 @@
     <t>Premium Beds</t>
   </si>
   <si>
-    <t>"Hey, Check this our new premium collections of the Beds"</t>
-  </si>
-  <si>
     <t>Premium Chairs</t>
   </si>
   <si>
@@ -545,9 +539,6 @@
   </si>
   <si>
     <t>Premium Mats</t>
-  </si>
-  <si>
-    <t>"Hey,Premium matt collection, please Check this"</t>
   </si>
   <si>
     <t>https://www.ikea.com/sa/en/images/products/varvial-fitted-sheet-blue__1243833_pe920981_s5.jpg</t>
@@ -1541,6 +1532,9 @@
   </si>
   <si>
     <t>嗨，我是莎拉。现在我们来到了第二间卧室——让我们来探索一下Illus照明如何凭借其高显色指数，展现出您空间的真实色彩。</t>
+  </si>
+  <si>
+    <t>"Hey, Check this our new premium collections of the Sofas"</t>
   </si>
 </sst>
 </file>
@@ -2752,18 +2746,18 @@
         <v>24</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="AA1" s="1" t="s">
         <v>25</v>
       </c>
       <c r="AB1" s="60" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" spans="1:28" ht="18.3" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>27</v>
@@ -2775,25 +2769,25 @@
         <v>1</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F2" s="38" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="G2" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H2" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I2" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J2" s="62" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="K2" s="62" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>31</v>
@@ -2826,10 +2820,10 @@
         <v>1</v>
       </c>
       <c r="V2" s="75" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="W2" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="X2" s="10" t="b">
         <v>1</v>
@@ -2838,18 +2832,18 @@
         <v>1</v>
       </c>
       <c r="Z2" s="68" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AA2" s="12">
         <v>45750</v>
       </c>
       <c r="AB2" s="72" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:28" ht="20.25" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>27</v>
@@ -2861,16 +2855,16 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F3" s="38" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G3" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H3" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I3" s="13" t="b">
         <v>0</v>
@@ -2912,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="V3" s="75" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="W3" s="11" t="s">
         <v>37</v>
@@ -2924,18 +2918,18 @@
         <v>1</v>
       </c>
       <c r="Z3" s="76" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="AA3" s="12">
         <v>45750</v>
       </c>
       <c r="AB3" s="72" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:28" ht="20.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>27</v>
@@ -2947,16 +2941,16 @@
         <v>3</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F4" s="38" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="G4" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H4" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I4" s="3" t="b">
         <v>1</v>
@@ -3011,12 +3005,12 @@
         <v>45750</v>
       </c>
       <c r="AB4" s="72" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="20.25" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>27</v>
@@ -3028,16 +3022,16 @@
         <v>4</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="F5" s="38" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="G5" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H5" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I5" s="3" t="b">
         <v>1</v>
@@ -3093,12 +3087,12 @@
         <v>45750</v>
       </c>
       <c r="AB5" s="72" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
     </row>
     <row r="6" spans="1:28" ht="20.25" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>27</v>
@@ -3110,16 +3104,16 @@
         <v>5</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F6" s="38" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G6" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H6" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I6" s="3" t="b">
         <v>1</v>
@@ -3175,12 +3169,12 @@
         <v>45750</v>
       </c>
       <c r="AB6" s="72" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="20.25" customHeight="1">
       <c r="A7" s="3" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>48</v>
@@ -3192,22 +3186,22 @@
         <v>7</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F7" s="38" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="G7" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H7" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I7" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J7" s="16" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>50</v>
@@ -3257,12 +3251,12 @@
         <v>45750</v>
       </c>
       <c r="AB7" s="72" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:28" ht="20.25" customHeight="1">
       <c r="A8" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>48</v>
@@ -3274,22 +3268,22 @@
         <v>6</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="F8" s="38" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G8" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H8" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I8" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J8" s="16" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>30</v>
@@ -3328,7 +3322,7 @@
         <v>33</v>
       </c>
       <c r="W8" s="11" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="X8" s="15" t="b">
         <v>0</v>
@@ -3341,12 +3335,12 @@
         <v>45750</v>
       </c>
       <c r="AB8" s="71" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:28" ht="20.25" customHeight="1">
       <c r="A9" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>48</v>
@@ -3358,22 +3352,22 @@
         <v>8</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="F9" s="38" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="G9" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H9" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I9" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J9" s="16" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>57</v>
@@ -3425,12 +3419,12 @@
         <v>45750</v>
       </c>
       <c r="AB9" s="71" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:28" ht="20.25" customHeight="1">
       <c r="A10" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>48</v>
@@ -3442,16 +3436,16 @@
         <v>9</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F10" s="38" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G10" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H10" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I10" s="3" t="b">
         <v>1</v>
@@ -3509,12 +3503,12 @@
         <v>45750</v>
       </c>
       <c r="AB10" s="71" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:28" ht="20.25" customHeight="1">
       <c r="A11" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>48</v>
@@ -3526,16 +3520,16 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F11" s="38" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="G11" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H11" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I11" s="3" t="b">
         <v>1</v>
@@ -3591,12 +3585,12 @@
         <v>45750</v>
       </c>
       <c r="AB11" s="71" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:28" ht="20.25" customHeight="1">
       <c r="A12" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>48</v>
@@ -3608,16 +3602,16 @@
         <v>11</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F12" s="38" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="G12" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H12" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I12" s="3" t="b">
         <v>1</v>
@@ -3675,12 +3669,12 @@
         <v>45750</v>
       </c>
       <c r="AB12" s="71" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:28" ht="20.25" customHeight="1">
       <c r="A13" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>72</v>
@@ -3692,16 +3686,16 @@
         <v>12</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F13" s="38" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G13" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H13" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I13" s="3" t="b">
         <v>1</v>
@@ -3759,12 +3753,12 @@
         <v>45750</v>
       </c>
       <c r="AB13" s="71" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="14" spans="1:28" ht="20.25" customHeight="1">
       <c r="A14" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>72</v>
@@ -3776,16 +3770,16 @@
         <v>13</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F14" s="38" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="G14" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H14" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I14" s="3" t="b">
         <v>1</v>
@@ -3843,12 +3837,12 @@
         <v>45750</v>
       </c>
       <c r="AB14" s="71" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" spans="1:28" ht="20.25" customHeight="1">
       <c r="A15" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>72</v>
@@ -3860,16 +3854,16 @@
         <v>14</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F15" s="38" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="G15" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H15" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I15" s="3" t="b">
         <v>1</v>
@@ -3927,12 +3921,12 @@
         <v>45750</v>
       </c>
       <c r="AB15" s="71" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="16" spans="1:28" ht="20.25" customHeight="1">
       <c r="A16" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>27</v>
@@ -3944,16 +3938,16 @@
         <v>15</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F16" s="38" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G16" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H16" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I16" s="13" t="b">
         <v>0</v>
@@ -4011,12 +4005,12 @@
         <v>45750</v>
       </c>
       <c r="AB16" s="71" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17" spans="1:28" ht="20.25" customHeight="1">
       <c r="A17" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>27</v>
@@ -4028,16 +4022,16 @@
         <v>16</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F17" s="38" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G17" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H17" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I17" s="3" t="b">
         <v>1</v>
@@ -4095,12 +4089,12 @@
         <v>45750</v>
       </c>
       <c r="AB17" s="71" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="18" spans="1:28" ht="20.25" customHeight="1">
       <c r="A18" s="3" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>27</v>
@@ -4112,16 +4106,16 @@
         <v>17</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F18" s="38" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="G18" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H18" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I18" s="3" t="b">
         <v>1</v>
@@ -4179,12 +4173,12 @@
         <v>45750</v>
       </c>
       <c r="AB18" s="71" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" spans="1:28" ht="20.25" customHeight="1">
       <c r="A19" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>93</v>
@@ -4196,22 +4190,22 @@
         <v>18</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="F19" s="38" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G19" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H19" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I19" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J19" s="16" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="K19" s="5" t="s">
         <v>95</v>
@@ -4263,12 +4257,12 @@
         <v>45750</v>
       </c>
       <c r="AB19" s="73" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
     <row r="20" spans="1:28" ht="20.25" customHeight="1">
       <c r="A20" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>93</v>
@@ -4280,22 +4274,22 @@
         <v>19</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F20" s="38" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="G20" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H20" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I20" s="3" t="b">
         <v>1</v>
       </c>
       <c r="J20" s="16" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="K20" s="5" t="s">
         <v>30</v>
@@ -4347,12 +4341,12 @@
         <v>45750</v>
       </c>
       <c r="AB20" s="73" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="21" spans="1:28" ht="20.25" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>93</v>
@@ -4364,16 +4358,16 @@
         <v>20</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F21" s="38" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="G21" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H21" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I21" s="3" t="b">
         <v>1</v>
@@ -4431,12 +4425,12 @@
         <v>45750</v>
       </c>
       <c r="AB21" s="73" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:28" ht="20.25" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>93</v>
@@ -4448,16 +4442,16 @@
         <v>21</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F22" s="38" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="G22" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H22" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I22" s="3" t="b">
         <v>1</v>
@@ -4515,12 +4509,12 @@
         <v>45750</v>
       </c>
       <c r="AB22" s="73" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="23" spans="1:28" ht="20.25" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>93</v>
@@ -4532,16 +4526,16 @@
         <v>22</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F23" s="38" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="G23" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H23" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I23" s="3" t="b">
         <v>1</v>
@@ -4595,18 +4589,18 @@
         <v>1</v>
       </c>
       <c r="Z23" s="76" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="AA23" s="12">
         <v>45750</v>
       </c>
       <c r="AB23" s="37" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="24" spans="1:28" ht="12" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>93</v>
@@ -4618,16 +4612,16 @@
         <v>23</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="F24" s="38" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G24" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H24" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I24" s="3" t="b">
         <v>1</v>
@@ -4685,33 +4679,33 @@
         <v>45750</v>
       </c>
       <c r="AB24" s="37" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" spans="1:28" ht="12" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D25" s="4">
         <v>24</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="F25" s="38" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G25" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H25" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I25" s="3" t="b">
         <v>1</v>
@@ -4747,7 +4741,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="9" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="U25" s="9" t="b">
         <v>1</v>
@@ -4756,7 +4750,7 @@
         <v>85</v>
       </c>
       <c r="W25" s="11" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="X25" s="10" t="b">
         <v>1</v>
@@ -4769,33 +4763,33 @@
         <v>45750</v>
       </c>
       <c r="AB25" s="37" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" spans="1:28" ht="12" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D26" s="4">
         <v>25</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G26" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H26" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I26" s="3" t="b">
         <v>1</v>
@@ -4831,7 +4825,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="9" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="U26" s="9" t="b">
         <v>1</v>
@@ -4840,7 +4834,7 @@
         <v>85</v>
       </c>
       <c r="W26" s="11" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="X26" s="10" t="b">
         <v>1</v>
@@ -4853,33 +4847,33 @@
         <v>45750</v>
       </c>
       <c r="AB26" s="37" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="27" spans="1:28" ht="12" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D27" s="4">
         <v>26</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G27" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H27" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I27" s="3" t="b">
         <v>1</v>
@@ -4915,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="9" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="U27" s="9" t="b">
         <v>1</v>
@@ -4924,7 +4918,7 @@
         <v>85</v>
       </c>
       <c r="W27" s="11" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="X27" s="10" t="b">
         <v>1</v>
@@ -4937,33 +4931,33 @@
         <v>45750</v>
       </c>
       <c r="AB27" s="37" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="28" spans="1:28" ht="12" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D28" s="4">
         <v>27</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G28" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H28" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I28" s="3" t="b">
         <v>1</v>
@@ -4999,7 +4993,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="9" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="U28" s="9" t="b">
         <v>1</v>
@@ -5021,33 +5015,33 @@
         <v>45750</v>
       </c>
       <c r="AB28" s="37" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" spans="1:28" ht="12" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D29" s="4">
         <v>28</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="G29" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H29" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I29" s="3" t="b">
         <v>1</v>
@@ -5083,7 +5077,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="9" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="U29" s="9" t="b">
         <v>1</v>
@@ -5092,7 +5086,7 @@
         <v>85</v>
       </c>
       <c r="W29" s="11" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="X29" s="10" t="b">
         <v>1</v>
@@ -5105,33 +5099,33 @@
         <v>45750</v>
       </c>
       <c r="AB29" s="37" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
     </row>
     <row r="30" spans="1:28" ht="12" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D30" s="4">
         <v>29</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F30" s="38" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="G30" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H30" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I30" s="3" t="b">
         <v>1</v>
@@ -5167,7 +5161,7 @@
         <v>1</v>
       </c>
       <c r="T30" s="9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="U30" s="9" t="b">
         <v>1</v>
@@ -5176,7 +5170,7 @@
         <v>85</v>
       </c>
       <c r="W30" s="11" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="X30" s="10" t="b">
         <v>1</v>
@@ -5189,33 +5183,33 @@
         <v>45750</v>
       </c>
       <c r="AB30" s="37" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31" spans="1:28" ht="12" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D31" s="4">
         <v>30</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="F31" s="38" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="G31" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H31" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I31" s="3" t="b">
         <v>1</v>
@@ -5251,7 +5245,7 @@
         <v>1</v>
       </c>
       <c r="T31" s="9" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="U31" s="9" t="b">
         <v>1</v>
@@ -5260,7 +5254,7 @@
         <v>85</v>
       </c>
       <c r="W31" s="11" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="X31" s="10" t="b">
         <v>1</v>
@@ -5273,33 +5267,33 @@
         <v>45750</v>
       </c>
       <c r="AB31" s="37" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" spans="1:28" ht="12" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>93</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D32" s="4">
         <v>31</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="F32" s="38" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G32" s="38" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H32" s="62" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="I32" s="3" t="b">
         <v>1</v>
@@ -5335,7 +5329,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="9" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="U32" s="9" t="b">
         <v>1</v>
@@ -5344,7 +5338,7 @@
         <v>85</v>
       </c>
       <c r="W32" s="11" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="X32" s="10" t="b">
         <v>1</v>
@@ -5357,7 +5351,7 @@
         <v>45750</v>
       </c>
       <c r="AB32" s="37" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="33" spans="4:14" ht="12" customHeight="1">
@@ -10299,16 +10293,16 @@
         <v>123</v>
       </c>
       <c r="L1" s="21" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="M1" s="21" t="s">
         <v>132</v>
       </c>
       <c r="N1" s="34" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="O1" s="63" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="P1" s="22"/>
       <c r="Q1" s="22"/>
@@ -10328,7 +10322,7 @@
         <v>32</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>134</v>
@@ -10354,7 +10348,7 @@
       </c>
       <c r="N2" s="35"/>
       <c r="O2" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q2"/>
     </row>
@@ -10372,7 +10366,7 @@
         <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>134</v>
@@ -10398,7 +10392,7 @@
       </c>
       <c r="N3" s="35"/>
       <c r="O3" s="57" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="Q3"/>
     </row>
@@ -10416,7 +10410,7 @@
         <v>32</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>134</v>
@@ -10442,7 +10436,7 @@
       </c>
       <c r="N4" s="35"/>
       <c r="O4" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q4"/>
     </row>
@@ -10460,7 +10454,7 @@
         <v>32</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>134</v>
@@ -10486,7 +10480,7 @@
       </c>
       <c r="N5" s="7"/>
       <c r="O5" s="57" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q5"/>
     </row>
@@ -10504,7 +10498,7 @@
         <v>32</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>134</v>
@@ -10528,7 +10522,7 @@
       </c>
       <c r="N6" s="7"/>
       <c r="O6" s="57" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q6"/>
     </row>
@@ -10546,7 +10540,7 @@
         <v>32</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>134</v>
@@ -10570,7 +10564,7 @@
       </c>
       <c r="N7" s="7"/>
       <c r="O7" s="57" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q7"/>
     </row>
@@ -10588,7 +10582,7 @@
         <v>32</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>134</v>
@@ -10612,7 +10606,7 @@
       </c>
       <c r="N8" s="7"/>
       <c r="O8" s="57" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="Q8"/>
     </row>
@@ -10630,10 +10624,10 @@
         <v>32</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="3" t="s">
@@ -10649,7 +10643,7 @@
         <v>141</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="M9" s="3" t="b">
         <v>1</v>
@@ -10671,10 +10665,10 @@
         <v>32</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="3" t="s">
@@ -10690,7 +10684,7 @@
         <v>141</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="M10" s="3" t="b">
         <v>1</v>
@@ -10712,7 +10706,7 @@
         <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>139</v>
@@ -10731,7 +10725,7 @@
         <v>141</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="M11" s="3" t="b">
         <v>1</v>
@@ -10755,7 +10749,7 @@
         <v>32</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>139</v>
@@ -10774,7 +10768,7 @@
         <v>141</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="M12" s="3" t="b">
         <v>1</v>
@@ -10798,7 +10792,7 @@
         <v>32</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>139</v>
@@ -10817,7 +10811,7 @@
         <v>141</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M13" s="3" t="b">
         <v>1</v>
@@ -10841,7 +10835,7 @@
         <v>32</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>139</v>
@@ -10860,7 +10854,7 @@
         <v>141</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M14" s="3" t="b">
         <v>1</v>
@@ -10884,7 +10878,7 @@
         <v>32</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>139</v>
@@ -10903,7 +10897,7 @@
         <v>141</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="M15" s="3" t="b">
         <v>1</v>
@@ -10927,7 +10921,7 @@
         <v>32</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>139</v>
@@ -10946,7 +10940,7 @@
         <v>141</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M16" s="3" t="b">
         <v>1</v>
@@ -10970,7 +10964,7 @@
         <v>32</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>139</v>
@@ -10989,7 +10983,7 @@
         <v>141</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M17" s="3" t="b">
         <v>1</v>
@@ -11013,7 +11007,7 @@
         <v>32</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>139</v>
@@ -11032,7 +11026,7 @@
         <v>141</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M18" s="3" t="b">
         <v>1</v>
@@ -11056,7 +11050,7 @@
         <v>32</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>139</v>
@@ -11075,7 +11069,7 @@
         <v>141</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M19" s="3" t="b">
         <v>1</v>
@@ -11099,7 +11093,7 @@
         <v>32</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>139</v>
@@ -11118,7 +11112,7 @@
         <v>141</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M20" s="3" t="b">
         <v>1</v>
@@ -11142,7 +11136,7 @@
         <v>36</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>134</v>
@@ -11168,7 +11162,7 @@
       </c>
       <c r="N21" s="35"/>
       <c r="O21" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q21"/>
     </row>
@@ -11186,7 +11180,7 @@
         <v>36</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>134</v>
@@ -11212,7 +11206,7 @@
       </c>
       <c r="N22" s="35"/>
       <c r="O22" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q22"/>
     </row>
@@ -11230,7 +11224,7 @@
         <v>36</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>139</v>
@@ -11249,7 +11243,7 @@
         <v>141</v>
       </c>
       <c r="L23" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M23" s="3" t="b">
         <v>1</v>
@@ -11272,7 +11266,7 @@
         <v>36</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>139</v>
@@ -11291,7 +11285,7 @@
         <v>141</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M24" s="3" t="b">
         <v>1</v>
@@ -11313,7 +11307,7 @@
         <v>36</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>139</v>
@@ -11332,7 +11326,7 @@
         <v>141</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M25" s="3" t="b">
         <v>1</v>
@@ -11354,7 +11348,7 @@
         <v>36</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>139</v>
@@ -11373,7 +11367,7 @@
         <v>141</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M26" s="3" t="b">
         <v>1</v>
@@ -11395,7 +11389,7 @@
         <v>36</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>139</v>
@@ -11414,7 +11408,7 @@
         <v>141</v>
       </c>
       <c r="L27" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M27" s="3" t="b">
         <v>1</v>
@@ -11436,7 +11430,7 @@
         <v>39</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>134</v>
@@ -11462,7 +11456,7 @@
       </c>
       <c r="N28" s="35"/>
       <c r="O28" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q28"/>
     </row>
@@ -11480,7 +11474,7 @@
         <v>39</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>134</v>
@@ -11506,7 +11500,7 @@
       </c>
       <c r="N29" s="35"/>
       <c r="O29" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q29"/>
     </row>
@@ -11524,7 +11518,7 @@
         <v>39</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>139</v>
@@ -11543,7 +11537,7 @@
         <v>141</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M30" s="3" t="b">
         <v>1</v>
@@ -11565,7 +11559,7 @@
         <v>39</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>139</v>
@@ -11584,7 +11578,7 @@
         <v>141</v>
       </c>
       <c r="L31" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M31" s="3" t="b">
         <v>1</v>
@@ -11606,7 +11600,7 @@
         <v>39</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>139</v>
@@ -11625,7 +11619,7 @@
         <v>141</v>
       </c>
       <c r="L32" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M32" s="3" t="b">
         <v>1</v>
@@ -11647,7 +11641,7 @@
         <v>39</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>139</v>
@@ -11666,7 +11660,7 @@
         <v>141</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M33" s="3" t="b">
         <v>1</v>
@@ -11688,7 +11682,7 @@
         <v>39</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>139</v>
@@ -11707,7 +11701,7 @@
         <v>141</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M34" s="3" t="b">
         <v>1</v>
@@ -11729,7 +11723,7 @@
         <v>43</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>134</v>
@@ -11755,7 +11749,7 @@
       </c>
       <c r="N35" s="35"/>
       <c r="O35" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q35"/>
     </row>
@@ -11773,7 +11767,7 @@
         <v>43</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>134</v>
@@ -11799,7 +11793,7 @@
       </c>
       <c r="N36" s="35"/>
       <c r="O36" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q36"/>
     </row>
@@ -11817,7 +11811,7 @@
         <v>43</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>139</v>
@@ -11836,7 +11830,7 @@
         <v>141</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M37" s="3" t="b">
         <v>1</v>
@@ -11858,7 +11852,7 @@
         <v>43</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>139</v>
@@ -11877,7 +11871,7 @@
         <v>141</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M38" s="3" t="b">
         <v>1</v>
@@ -11899,7 +11893,7 @@
         <v>43</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>139</v>
@@ -11918,7 +11912,7 @@
         <v>141</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M39" s="3" t="b">
         <v>1</v>
@@ -11940,7 +11934,7 @@
         <v>43</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>139</v>
@@ -11959,7 +11953,7 @@
         <v>141</v>
       </c>
       <c r="L40" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M40" s="3" t="b">
         <v>1</v>
@@ -11981,7 +11975,7 @@
         <v>43</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>139</v>
@@ -12000,7 +11994,7 @@
         <v>141</v>
       </c>
       <c r="L41" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M41" s="3" t="b">
         <v>1</v>
@@ -12022,7 +12016,7 @@
         <v>46</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>134</v>
@@ -12048,7 +12042,7 @@
       </c>
       <c r="N42" s="35"/>
       <c r="O42" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q42"/>
     </row>
@@ -12066,7 +12060,7 @@
         <v>46</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>134</v>
@@ -12092,7 +12086,7 @@
       </c>
       <c r="N43" s="35"/>
       <c r="O43" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q43"/>
     </row>
@@ -12110,7 +12104,7 @@
         <v>46</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>139</v>
@@ -12129,7 +12123,7 @@
         <v>141</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M44" s="3" t="b">
         <v>1</v>
@@ -12151,7 +12145,7 @@
         <v>46</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>139</v>
@@ -12170,7 +12164,7 @@
         <v>141</v>
       </c>
       <c r="L45" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M45" s="3" t="b">
         <v>1</v>
@@ -12192,7 +12186,7 @@
         <v>46</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>139</v>
@@ -12211,7 +12205,7 @@
         <v>141</v>
       </c>
       <c r="L46" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M46" s="3" t="b">
         <v>1</v>
@@ -12233,7 +12227,7 @@
         <v>46</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>139</v>
@@ -12252,7 +12246,7 @@
         <v>141</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M47" s="3" t="b">
         <v>1</v>
@@ -12274,7 +12268,7 @@
         <v>46</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>139</v>
@@ -12293,7 +12287,7 @@
         <v>141</v>
       </c>
       <c r="L48" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M48" s="3" t="b">
         <v>1</v>
@@ -12315,7 +12309,7 @@
         <v>52</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>134</v>
@@ -12341,7 +12335,7 @@
       </c>
       <c r="N49" s="35"/>
       <c r="O49" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q49"/>
     </row>
@@ -12359,7 +12353,7 @@
         <v>52</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>134</v>
@@ -12385,7 +12379,7 @@
       </c>
       <c r="N50" s="35"/>
       <c r="O50" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q50"/>
     </row>
@@ -12403,7 +12397,7 @@
         <v>52</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>139</v>
@@ -12422,7 +12416,7 @@
         <v>141</v>
       </c>
       <c r="L51" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M51" s="3" t="b">
         <v>1</v>
@@ -12444,7 +12438,7 @@
         <v>52</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>139</v>
@@ -12463,7 +12457,7 @@
         <v>141</v>
       </c>
       <c r="L52" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M52" s="3" t="b">
         <v>1</v>
@@ -12485,7 +12479,7 @@
         <v>52</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>139</v>
@@ -12504,7 +12498,7 @@
         <v>141</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M53" s="3" t="b">
         <v>1</v>
@@ -12526,7 +12520,7 @@
         <v>52</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>139</v>
@@ -12545,7 +12539,7 @@
         <v>141</v>
       </c>
       <c r="L54" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M54" s="3" t="b">
         <v>1</v>
@@ -12567,7 +12561,7 @@
         <v>52</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>139</v>
@@ -12586,7 +12580,7 @@
         <v>141</v>
       </c>
       <c r="L55" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M55" s="3" t="b">
         <v>1</v>
@@ -12608,7 +12602,7 @@
         <v>55</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>134</v>
@@ -12634,7 +12628,7 @@
       </c>
       <c r="N56" s="35"/>
       <c r="O56" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q56"/>
     </row>
@@ -12652,7 +12646,7 @@
         <v>55</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>134</v>
@@ -12678,7 +12672,7 @@
       </c>
       <c r="N57" s="35"/>
       <c r="O57" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q57"/>
     </row>
@@ -12696,7 +12690,7 @@
         <v>55</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>139</v>
@@ -12715,7 +12709,7 @@
         <v>141</v>
       </c>
       <c r="L58" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M58" s="3" t="b">
         <v>1</v>
@@ -12737,7 +12731,7 @@
         <v>55</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>139</v>
@@ -12756,7 +12750,7 @@
         <v>141</v>
       </c>
       <c r="L59" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M59" s="3" t="b">
         <v>1</v>
@@ -12778,7 +12772,7 @@
         <v>55</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>139</v>
@@ -12797,7 +12791,7 @@
         <v>141</v>
       </c>
       <c r="L60" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M60" s="3" t="b">
         <v>1</v>
@@ -12819,7 +12813,7 @@
         <v>55</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>139</v>
@@ -12838,7 +12832,7 @@
         <v>141</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M61" s="3" t="b">
         <v>1</v>
@@ -12860,7 +12854,7 @@
         <v>55</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>139</v>
@@ -12879,7 +12873,7 @@
         <v>141</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M62" s="3" t="b">
         <v>1</v>
@@ -12901,7 +12895,7 @@
         <v>59</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>134</v>
@@ -12927,7 +12921,7 @@
       </c>
       <c r="N63" s="35"/>
       <c r="O63" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q63"/>
     </row>
@@ -12945,7 +12939,7 @@
         <v>59</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>134</v>
@@ -12971,7 +12965,7 @@
       </c>
       <c r="N64" s="35"/>
       <c r="O64" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q64"/>
     </row>
@@ -12989,7 +12983,7 @@
         <v>59</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>139</v>
@@ -13008,7 +13002,7 @@
         <v>141</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M65" s="3" t="b">
         <v>1</v>
@@ -13030,7 +13024,7 @@
         <v>59</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>139</v>
@@ -13049,7 +13043,7 @@
         <v>141</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M66" s="3" t="b">
         <v>1</v>
@@ -13071,7 +13065,7 @@
         <v>59</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>139</v>
@@ -13090,7 +13084,7 @@
         <v>141</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M67" s="3" t="b">
         <v>1</v>
@@ -13112,7 +13106,7 @@
         <v>59</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>139</v>
@@ -13131,7 +13125,7 @@
         <v>141</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M68" s="3" t="b">
         <v>1</v>
@@ -13153,7 +13147,7 @@
         <v>59</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>139</v>
@@ -13172,7 +13166,7 @@
         <v>141</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M69" s="3" t="b">
         <v>1</v>
@@ -13194,7 +13188,7 @@
         <v>63</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>134</v>
@@ -13220,7 +13214,7 @@
       </c>
       <c r="N70" s="35"/>
       <c r="O70" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q70"/>
     </row>
@@ -13238,7 +13232,7 @@
         <v>63</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>134</v>
@@ -13264,7 +13258,7 @@
       </c>
       <c r="N71" s="35"/>
       <c r="O71" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q71"/>
     </row>
@@ -13282,7 +13276,7 @@
         <v>63</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>139</v>
@@ -13301,7 +13295,7 @@
         <v>141</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M72" s="3" t="b">
         <v>1</v>
@@ -13323,7 +13317,7 @@
         <v>63</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>139</v>
@@ -13342,7 +13336,7 @@
         <v>141</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M73" s="3" t="b">
         <v>1</v>
@@ -13364,7 +13358,7 @@
         <v>63</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>139</v>
@@ -13383,7 +13377,7 @@
         <v>141</v>
       </c>
       <c r="L74" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M74" s="3" t="b">
         <v>1</v>
@@ -13405,7 +13399,7 @@
         <v>63</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>139</v>
@@ -13424,7 +13418,7 @@
         <v>141</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M75" s="3" t="b">
         <v>1</v>
@@ -13446,7 +13440,7 @@
         <v>63</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>139</v>
@@ -13465,7 +13459,7 @@
         <v>141</v>
       </c>
       <c r="L76" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M76" s="3" t="b">
         <v>1</v>
@@ -13487,7 +13481,7 @@
         <v>66</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>134</v>
@@ -13513,7 +13507,7 @@
       </c>
       <c r="N77" s="35"/>
       <c r="O77" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q77"/>
     </row>
@@ -13531,7 +13525,7 @@
         <v>66</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>134</v>
@@ -13557,7 +13551,7 @@
       </c>
       <c r="N78" s="35"/>
       <c r="O78" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q78"/>
     </row>
@@ -13575,7 +13569,7 @@
         <v>66</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>139</v>
@@ -13594,7 +13588,7 @@
         <v>141</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M79" s="3" t="b">
         <v>1</v>
@@ -13616,7 +13610,7 @@
         <v>66</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>139</v>
@@ -13635,7 +13629,7 @@
         <v>141</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M80" s="3" t="b">
         <v>1</v>
@@ -13657,7 +13651,7 @@
         <v>66</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>139</v>
@@ -13676,7 +13670,7 @@
         <v>141</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M81" s="3" t="b">
         <v>1</v>
@@ -13698,7 +13692,7 @@
         <v>66</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>139</v>
@@ -13717,7 +13711,7 @@
         <v>141</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M82" s="3" t="b">
         <v>1</v>
@@ -13739,7 +13733,7 @@
         <v>66</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>139</v>
@@ -13758,7 +13752,7 @@
         <v>141</v>
       </c>
       <c r="L83" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M83" s="3" t="b">
         <v>1</v>
@@ -13780,7 +13774,7 @@
         <v>69</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>134</v>
@@ -13806,7 +13800,7 @@
       </c>
       <c r="N84" s="35"/>
       <c r="O84" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q84"/>
     </row>
@@ -13824,7 +13818,7 @@
         <v>69</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>134</v>
@@ -13850,7 +13844,7 @@
       </c>
       <c r="N85" s="35"/>
       <c r="O85" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q85"/>
     </row>
@@ -13868,7 +13862,7 @@
         <v>69</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>139</v>
@@ -13887,7 +13881,7 @@
         <v>141</v>
       </c>
       <c r="L86" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M86" s="3" t="b">
         <v>1</v>
@@ -13909,7 +13903,7 @@
         <v>69</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F87" s="3" t="s">
         <v>139</v>
@@ -13928,7 +13922,7 @@
         <v>141</v>
       </c>
       <c r="L87" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M87" s="3" t="b">
         <v>1</v>
@@ -13950,7 +13944,7 @@
         <v>69</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>139</v>
@@ -13969,7 +13963,7 @@
         <v>141</v>
       </c>
       <c r="L88" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M88" s="3" t="b">
         <v>1</v>
@@ -13991,7 +13985,7 @@
         <v>69</v>
       </c>
       <c r="E89" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F89" s="3" t="s">
         <v>139</v>
@@ -14010,7 +14004,7 @@
         <v>141</v>
       </c>
       <c r="L89" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M89" s="3" t="b">
         <v>1</v>
@@ -14032,7 +14026,7 @@
         <v>69</v>
       </c>
       <c r="E90" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>139</v>
@@ -14051,7 +14045,7 @@
         <v>141</v>
       </c>
       <c r="L90" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M90" s="3" t="b">
         <v>1</v>
@@ -14073,7 +14067,7 @@
         <v>74</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F91" s="3" t="s">
         <v>134</v>
@@ -14099,7 +14093,7 @@
       </c>
       <c r="N91" s="35"/>
       <c r="O91" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q91"/>
     </row>
@@ -14117,7 +14111,7 @@
         <v>74</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>134</v>
@@ -14143,7 +14137,7 @@
       </c>
       <c r="N92" s="35"/>
       <c r="O92" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q92"/>
     </row>
@@ -14161,7 +14155,7 @@
         <v>74</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F93" s="3" t="s">
         <v>139</v>
@@ -14180,7 +14174,7 @@
         <v>141</v>
       </c>
       <c r="L93" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M93" s="3" t="b">
         <v>1</v>
@@ -14202,7 +14196,7 @@
         <v>74</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>139</v>
@@ -14221,7 +14215,7 @@
         <v>141</v>
       </c>
       <c r="L94" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M94" s="3" t="b">
         <v>1</v>
@@ -14243,7 +14237,7 @@
         <v>74</v>
       </c>
       <c r="E95" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F95" s="3" t="s">
         <v>139</v>
@@ -14262,7 +14256,7 @@
         <v>141</v>
       </c>
       <c r="L95" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M95" s="3" t="b">
         <v>1</v>
@@ -14284,7 +14278,7 @@
         <v>74</v>
       </c>
       <c r="E96" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>139</v>
@@ -14303,7 +14297,7 @@
         <v>141</v>
       </c>
       <c r="L96" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M96" s="3" t="b">
         <v>1</v>
@@ -14325,7 +14319,7 @@
         <v>74</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F97" s="3" t="s">
         <v>139</v>
@@ -14344,7 +14338,7 @@
         <v>141</v>
       </c>
       <c r="L97" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M97" s="3" t="b">
         <v>1</v>
@@ -14366,7 +14360,7 @@
         <v>77</v>
       </c>
       <c r="E98" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>134</v>
@@ -14392,7 +14386,7 @@
       </c>
       <c r="N98" s="35"/>
       <c r="O98" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q98"/>
     </row>
@@ -14410,7 +14404,7 @@
         <v>77</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F99" s="3" t="s">
         <v>134</v>
@@ -14436,7 +14430,7 @@
       </c>
       <c r="N99" s="35"/>
       <c r="O99" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q99"/>
     </row>
@@ -14454,7 +14448,7 @@
         <v>77</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>139</v>
@@ -14473,7 +14467,7 @@
         <v>141</v>
       </c>
       <c r="L100" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M100" s="3" t="b">
         <v>1</v>
@@ -14495,7 +14489,7 @@
         <v>77</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F101" s="3" t="s">
         <v>139</v>
@@ -14514,7 +14508,7 @@
         <v>141</v>
       </c>
       <c r="L101" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M101" s="3" t="b">
         <v>1</v>
@@ -14536,7 +14530,7 @@
         <v>77</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>139</v>
@@ -14555,7 +14549,7 @@
         <v>141</v>
       </c>
       <c r="L102" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M102" s="3" t="b">
         <v>1</v>
@@ -14577,7 +14571,7 @@
         <v>77</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F103" s="3" t="s">
         <v>139</v>
@@ -14596,7 +14590,7 @@
         <v>141</v>
       </c>
       <c r="L103" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M103" s="3" t="b">
         <v>1</v>
@@ -14618,7 +14612,7 @@
         <v>77</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>139</v>
@@ -14637,7 +14631,7 @@
         <v>141</v>
       </c>
       <c r="L104" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M104" s="3" t="b">
         <v>1</v>
@@ -14659,7 +14653,7 @@
         <v>80</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F105" s="3" t="s">
         <v>134</v>
@@ -14685,7 +14679,7 @@
       </c>
       <c r="N105" s="35"/>
       <c r="O105" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q105"/>
     </row>
@@ -14703,7 +14697,7 @@
         <v>80</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>134</v>
@@ -14729,7 +14723,7 @@
       </c>
       <c r="N106" s="35"/>
       <c r="O106" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q106"/>
     </row>
@@ -14747,7 +14741,7 @@
         <v>80</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F107" s="3" t="s">
         <v>139</v>
@@ -14766,7 +14760,7 @@
         <v>141</v>
       </c>
       <c r="L107" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M107" s="3" t="b">
         <v>1</v>
@@ -14788,7 +14782,7 @@
         <v>80</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>139</v>
@@ -14807,7 +14801,7 @@
         <v>141</v>
       </c>
       <c r="L108" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M108" s="3" t="b">
         <v>1</v>
@@ -14829,7 +14823,7 @@
         <v>80</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F109" s="3" t="s">
         <v>139</v>
@@ -14848,7 +14842,7 @@
         <v>141</v>
       </c>
       <c r="L109" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M109" s="3" t="b">
         <v>1</v>
@@ -14870,7 +14864,7 @@
         <v>80</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>139</v>
@@ -14889,7 +14883,7 @@
         <v>141</v>
       </c>
       <c r="L110" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M110" s="3" t="b">
         <v>1</v>
@@ -14911,7 +14905,7 @@
         <v>80</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F111" s="3" t="s">
         <v>139</v>
@@ -14930,7 +14924,7 @@
         <v>141</v>
       </c>
       <c r="L111" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M111" s="3" t="b">
         <v>1</v>
@@ -14940,7 +14934,7 @@
     </row>
     <row r="112" spans="1:17" ht="19.5" customHeight="1">
       <c r="A112" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B112" s="7">
         <v>15</v>
@@ -14952,7 +14946,7 @@
         <v>84</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>134</v>
@@ -14978,13 +14972,13 @@
       </c>
       <c r="N112" s="35"/>
       <c r="O112" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q112"/>
     </row>
     <row r="113" spans="1:17" ht="12" customHeight="1">
       <c r="A113" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B113" s="7">
         <v>15</v>
@@ -14996,7 +14990,7 @@
         <v>84</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F113" s="3" t="s">
         <v>134</v>
@@ -15022,13 +15016,13 @@
       </c>
       <c r="N113" s="35"/>
       <c r="O113" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q113"/>
     </row>
     <row r="114" spans="1:17" ht="12" customHeight="1">
       <c r="A114" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B114" s="7">
         <v>15</v>
@@ -15040,7 +15034,7 @@
         <v>84</v>
       </c>
       <c r="E114" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>139</v>
@@ -15059,7 +15053,7 @@
         <v>141</v>
       </c>
       <c r="L114" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M114" s="3" t="b">
         <v>1</v>
@@ -15069,7 +15063,7 @@
     </row>
     <row r="115" spans="1:17" ht="12" customHeight="1">
       <c r="A115" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B115" s="7">
         <v>15</v>
@@ -15081,7 +15075,7 @@
         <v>84</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F115" s="3" t="s">
         <v>139</v>
@@ -15100,7 +15094,7 @@
         <v>141</v>
       </c>
       <c r="L115" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M115" s="3" t="b">
         <v>1</v>
@@ -15110,7 +15104,7 @@
     </row>
     <row r="116" spans="1:17" ht="12" customHeight="1">
       <c r="A116" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B116" s="7">
         <v>15</v>
@@ -15122,7 +15116,7 @@
         <v>84</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>139</v>
@@ -15141,7 +15135,7 @@
         <v>141</v>
       </c>
       <c r="L116" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M116" s="3" t="b">
         <v>1</v>
@@ -15151,7 +15145,7 @@
     </row>
     <row r="117" spans="1:17" ht="12" customHeight="1">
       <c r="A117" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B117" s="7">
         <v>15</v>
@@ -15163,7 +15157,7 @@
         <v>84</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F117" s="3" t="s">
         <v>139</v>
@@ -15182,7 +15176,7 @@
         <v>141</v>
       </c>
       <c r="L117" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M117" s="3" t="b">
         <v>1</v>
@@ -15192,7 +15186,7 @@
     </row>
     <row r="118" spans="1:17" ht="12" customHeight="1">
       <c r="A118" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B118" s="7">
         <v>15</v>
@@ -15204,7 +15198,7 @@
         <v>84</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>139</v>
@@ -15223,7 +15217,7 @@
         <v>141</v>
       </c>
       <c r="L118" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M118" s="3" t="b">
         <v>1</v>
@@ -15233,7 +15227,7 @@
     </row>
     <row r="119" spans="1:17" ht="19.5" customHeight="1">
       <c r="A119" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B119" s="7">
         <v>16</v>
@@ -15245,7 +15239,7 @@
         <v>88</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F119" s="3" t="s">
         <v>134</v>
@@ -15271,13 +15265,13 @@
       </c>
       <c r="N119" s="35"/>
       <c r="O119" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q119"/>
     </row>
     <row r="120" spans="1:17" ht="12" customHeight="1">
       <c r="A120" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B120" s="7">
         <v>16</v>
@@ -15289,7 +15283,7 @@
         <v>88</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F120" s="3" t="s">
         <v>134</v>
@@ -15315,13 +15309,13 @@
       </c>
       <c r="N120" s="35"/>
       <c r="O120" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q120"/>
     </row>
     <row r="121" spans="1:17" ht="12" customHeight="1">
       <c r="A121" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B121" s="7">
         <v>16</v>
@@ -15333,7 +15327,7 @@
         <v>88</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F121" s="3" t="s">
         <v>139</v>
@@ -15352,7 +15346,7 @@
         <v>141</v>
       </c>
       <c r="L121" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M121" s="3" t="b">
         <v>1</v>
@@ -15362,7 +15356,7 @@
     </row>
     <row r="122" spans="1:17" ht="12" customHeight="1">
       <c r="A122" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B122" s="7">
         <v>16</v>
@@ -15374,7 +15368,7 @@
         <v>88</v>
       </c>
       <c r="E122" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>139</v>
@@ -15393,7 +15387,7 @@
         <v>141</v>
       </c>
       <c r="L122" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M122" s="3" t="b">
         <v>1</v>
@@ -15403,7 +15397,7 @@
     </row>
     <row r="123" spans="1:17" ht="12" customHeight="1">
       <c r="A123" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B123" s="7">
         <v>16</v>
@@ -15415,7 +15409,7 @@
         <v>88</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F123" s="3" t="s">
         <v>139</v>
@@ -15434,7 +15428,7 @@
         <v>141</v>
       </c>
       <c r="L123" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M123" s="3" t="b">
         <v>1</v>
@@ -15444,7 +15438,7 @@
     </row>
     <row r="124" spans="1:17" ht="12" customHeight="1">
       <c r="A124" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B124" s="7">
         <v>16</v>
@@ -15456,7 +15450,7 @@
         <v>88</v>
       </c>
       <c r="E124" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>139</v>
@@ -15475,7 +15469,7 @@
         <v>141</v>
       </c>
       <c r="L124" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M124" s="3" t="b">
         <v>1</v>
@@ -15485,7 +15479,7 @@
     </row>
     <row r="125" spans="1:17" ht="12" customHeight="1">
       <c r="A125" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B125" s="7">
         <v>16</v>
@@ -15497,7 +15491,7 @@
         <v>88</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F125" s="3" t="s">
         <v>139</v>
@@ -15516,7 +15510,7 @@
         <v>141</v>
       </c>
       <c r="L125" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M125" s="3" t="b">
         <v>1</v>
@@ -15526,7 +15520,7 @@
     </row>
     <row r="126" spans="1:17" ht="19.5" customHeight="1">
       <c r="A126" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B126" s="7">
         <v>17</v>
@@ -15538,7 +15532,7 @@
         <v>91</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>134</v>
@@ -15564,13 +15558,13 @@
       </c>
       <c r="N126" s="35"/>
       <c r="O126" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q126"/>
     </row>
     <row r="127" spans="1:17" ht="12" customHeight="1">
       <c r="A127" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B127" s="7">
         <v>17</v>
@@ -15582,7 +15576,7 @@
         <v>91</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F127" s="3" t="s">
         <v>134</v>
@@ -15608,13 +15602,13 @@
       </c>
       <c r="N127" s="35"/>
       <c r="O127" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q127"/>
     </row>
     <row r="128" spans="1:17" ht="12" customHeight="1">
       <c r="A128" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B128" s="7">
         <v>17</v>
@@ -15626,7 +15620,7 @@
         <v>91</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>139</v>
@@ -15645,7 +15639,7 @@
         <v>141</v>
       </c>
       <c r="L128" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M128" s="3" t="b">
         <v>1</v>
@@ -15655,7 +15649,7 @@
     </row>
     <row r="129" spans="1:17" ht="12" customHeight="1">
       <c r="A129" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B129" s="7">
         <v>17</v>
@@ -15667,7 +15661,7 @@
         <v>91</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F129" s="3" t="s">
         <v>139</v>
@@ -15686,7 +15680,7 @@
         <v>141</v>
       </c>
       <c r="L129" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M129" s="3" t="b">
         <v>1</v>
@@ -15696,7 +15690,7 @@
     </row>
     <row r="130" spans="1:17" ht="12" customHeight="1">
       <c r="A130" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B130" s="7">
         <v>17</v>
@@ -15708,7 +15702,7 @@
         <v>91</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>139</v>
@@ -15727,7 +15721,7 @@
         <v>141</v>
       </c>
       <c r="L130" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M130" s="3" t="b">
         <v>1</v>
@@ -15737,7 +15731,7 @@
     </row>
     <row r="131" spans="1:17" ht="12" customHeight="1">
       <c r="A131" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B131" s="7">
         <v>17</v>
@@ -15749,7 +15743,7 @@
         <v>91</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F131" s="3" t="s">
         <v>139</v>
@@ -15768,7 +15762,7 @@
         <v>141</v>
       </c>
       <c r="L131" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M131" s="3" t="b">
         <v>1</v>
@@ -15778,7 +15772,7 @@
     </row>
     <row r="132" spans="1:17" ht="12" customHeight="1">
       <c r="A132" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B132" s="7">
         <v>17</v>
@@ -15790,7 +15784,7 @@
         <v>91</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>139</v>
@@ -15809,7 +15803,7 @@
         <v>141</v>
       </c>
       <c r="L132" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M132" s="3" t="b">
         <v>1</v>
@@ -15819,7 +15813,7 @@
     </row>
     <row r="133" spans="1:17" ht="19.5" customHeight="1">
       <c r="A133" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B133" s="7">
         <v>18</v>
@@ -15831,7 +15825,7 @@
         <v>97</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F133" s="3" t="s">
         <v>134</v>
@@ -15857,13 +15851,13 @@
       </c>
       <c r="N133" s="35"/>
       <c r="O133" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q133"/>
     </row>
     <row r="134" spans="1:17" ht="12" customHeight="1">
       <c r="A134" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B134" s="7">
         <v>18</v>
@@ -15875,7 +15869,7 @@
         <v>97</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>134</v>
@@ -15901,13 +15895,13 @@
       </c>
       <c r="N134" s="35"/>
       <c r="O134" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q134"/>
     </row>
     <row r="135" spans="1:17" ht="12" customHeight="1">
       <c r="A135" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B135" s="7">
         <v>18</v>
@@ -15919,7 +15913,7 @@
         <v>97</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F135" s="3" t="s">
         <v>139</v>
@@ -15938,7 +15932,7 @@
         <v>141</v>
       </c>
       <c r="L135" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M135" s="3" t="b">
         <v>1</v>
@@ -15948,7 +15942,7 @@
     </row>
     <row r="136" spans="1:17" ht="12" customHeight="1">
       <c r="A136" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B136" s="7">
         <v>18</v>
@@ -15960,7 +15954,7 @@
         <v>97</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>139</v>
@@ -15979,7 +15973,7 @@
         <v>141</v>
       </c>
       <c r="L136" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M136" s="3" t="b">
         <v>1</v>
@@ -15989,7 +15983,7 @@
     </row>
     <row r="137" spans="1:17" ht="12" customHeight="1">
       <c r="A137" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B137" s="7">
         <v>18</v>
@@ -16001,7 +15995,7 @@
         <v>97</v>
       </c>
       <c r="E137" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F137" s="3" t="s">
         <v>139</v>
@@ -16020,7 +16014,7 @@
         <v>141</v>
       </c>
       <c r="L137" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M137" s="3" t="b">
         <v>1</v>
@@ -16030,7 +16024,7 @@
     </row>
     <row r="138" spans="1:17" ht="12" customHeight="1">
       <c r="A138" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B138" s="7">
         <v>18</v>
@@ -16042,7 +16036,7 @@
         <v>97</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>139</v>
@@ -16061,7 +16055,7 @@
         <v>141</v>
       </c>
       <c r="L138" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M138" s="3" t="b">
         <v>1</v>
@@ -16071,7 +16065,7 @@
     </row>
     <row r="139" spans="1:17" ht="12" customHeight="1">
       <c r="A139" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B139" s="7">
         <v>18</v>
@@ -16083,7 +16077,7 @@
         <v>97</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F139" s="3" t="s">
         <v>139</v>
@@ -16102,7 +16096,7 @@
         <v>141</v>
       </c>
       <c r="L139" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M139" s="3" t="b">
         <v>1</v>
@@ -16112,7 +16106,7 @@
     </row>
     <row r="140" spans="1:17" ht="19.5" customHeight="1">
       <c r="A140" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B140" s="7">
         <v>19</v>
@@ -16124,7 +16118,7 @@
         <v>101</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>134</v>
@@ -16150,13 +16144,13 @@
       </c>
       <c r="N140" s="35"/>
       <c r="O140" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q140"/>
     </row>
     <row r="141" spans="1:17" ht="12" customHeight="1">
       <c r="A141" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B141" s="7">
         <v>19</v>
@@ -16168,7 +16162,7 @@
         <v>101</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F141" s="3" t="s">
         <v>134</v>
@@ -16194,13 +16188,13 @@
       </c>
       <c r="N141" s="35"/>
       <c r="O141" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q141"/>
     </row>
     <row r="142" spans="1:17" ht="12" customHeight="1">
       <c r="A142" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B142" s="7">
         <v>19</v>
@@ -16212,7 +16206,7 @@
         <v>101</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>139</v>
@@ -16231,7 +16225,7 @@
         <v>141</v>
       </c>
       <c r="L142" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M142" s="3" t="b">
         <v>1</v>
@@ -16241,7 +16235,7 @@
     </row>
     <row r="143" spans="1:17" ht="12" customHeight="1">
       <c r="A143" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B143" s="7">
         <v>19</v>
@@ -16253,7 +16247,7 @@
         <v>101</v>
       </c>
       <c r="E143" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F143" s="3" t="s">
         <v>139</v>
@@ -16272,7 +16266,7 @@
         <v>141</v>
       </c>
       <c r="L143" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M143" s="3" t="b">
         <v>1</v>
@@ -16282,7 +16276,7 @@
     </row>
     <row r="144" spans="1:17" ht="12" customHeight="1">
       <c r="A144" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B144" s="7">
         <v>19</v>
@@ -16294,7 +16288,7 @@
         <v>101</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>139</v>
@@ -16313,7 +16307,7 @@
         <v>141</v>
       </c>
       <c r="L144" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M144" s="3" t="b">
         <v>1</v>
@@ -16323,7 +16317,7 @@
     </row>
     <row r="145" spans="1:17" ht="12" customHeight="1">
       <c r="A145" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B145" s="7">
         <v>19</v>
@@ -16335,7 +16329,7 @@
         <v>101</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F145" s="3" t="s">
         <v>139</v>
@@ -16354,7 +16348,7 @@
         <v>141</v>
       </c>
       <c r="L145" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M145" s="3" t="b">
         <v>1</v>
@@ -16364,7 +16358,7 @@
     </row>
     <row r="146" spans="1:17" ht="12" customHeight="1">
       <c r="A146" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B146" s="7">
         <v>19</v>
@@ -16376,7 +16370,7 @@
         <v>101</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>139</v>
@@ -16395,7 +16389,7 @@
         <v>141</v>
       </c>
       <c r="L146" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M146" s="3" t="b">
         <v>1</v>
@@ -16405,7 +16399,7 @@
     </row>
     <row r="147" spans="1:17" ht="19.5" customHeight="1">
       <c r="A147" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B147" s="7">
         <v>20</v>
@@ -16417,7 +16411,7 @@
         <v>104</v>
       </c>
       <c r="E147" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F147" s="3" t="s">
         <v>134</v>
@@ -16443,13 +16437,13 @@
       </c>
       <c r="N147" s="35"/>
       <c r="O147" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q147"/>
     </row>
     <row r="148" spans="1:17" ht="12" customHeight="1">
       <c r="A148" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B148" s="7">
         <v>20</v>
@@ -16461,7 +16455,7 @@
         <v>104</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>134</v>
@@ -16487,13 +16481,13 @@
       </c>
       <c r="N148" s="35"/>
       <c r="O148" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q148"/>
     </row>
     <row r="149" spans="1:17" ht="12" customHeight="1">
       <c r="A149" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B149" s="7">
         <v>20</v>
@@ -16505,7 +16499,7 @@
         <v>104</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F149" s="3" t="s">
         <v>139</v>
@@ -16524,7 +16518,7 @@
         <v>141</v>
       </c>
       <c r="L149" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M149" s="3" t="b">
         <v>1</v>
@@ -16534,7 +16528,7 @@
     </row>
     <row r="150" spans="1:17" ht="12" customHeight="1">
       <c r="A150" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B150" s="7">
         <v>20</v>
@@ -16546,7 +16540,7 @@
         <v>104</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>139</v>
@@ -16565,7 +16559,7 @@
         <v>141</v>
       </c>
       <c r="L150" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M150" s="3" t="b">
         <v>1</v>
@@ -16575,7 +16569,7 @@
     </row>
     <row r="151" spans="1:17" ht="12" customHeight="1">
       <c r="A151" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B151" s="7">
         <v>20</v>
@@ -16587,7 +16581,7 @@
         <v>104</v>
       </c>
       <c r="E151" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F151" s="3" t="s">
         <v>139</v>
@@ -16606,7 +16600,7 @@
         <v>141</v>
       </c>
       <c r="L151" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M151" s="3" t="b">
         <v>1</v>
@@ -16616,7 +16610,7 @@
     </row>
     <row r="152" spans="1:17" ht="12" customHeight="1">
       <c r="A152" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B152" s="7">
         <v>20</v>
@@ -16628,7 +16622,7 @@
         <v>104</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>139</v>
@@ -16647,7 +16641,7 @@
         <v>141</v>
       </c>
       <c r="L152" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M152" s="3" t="b">
         <v>1</v>
@@ -16657,7 +16651,7 @@
     </row>
     <row r="153" spans="1:17" ht="12" customHeight="1">
       <c r="A153" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B153" s="7">
         <v>20</v>
@@ -16669,7 +16663,7 @@
         <v>104</v>
       </c>
       <c r="E153" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F153" s="3" t="s">
         <v>139</v>
@@ -16688,7 +16682,7 @@
         <v>141</v>
       </c>
       <c r="L153" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M153" s="3" t="b">
         <v>1</v>
@@ -16698,7 +16692,7 @@
     </row>
     <row r="154" spans="1:17" ht="19.5" customHeight="1">
       <c r="A154" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B154" s="7">
         <v>21</v>
@@ -16710,7 +16704,7 @@
         <v>107</v>
       </c>
       <c r="E154" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>134</v>
@@ -16736,13 +16730,13 @@
       </c>
       <c r="N154" s="35"/>
       <c r="O154" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q154"/>
     </row>
     <row r="155" spans="1:17" ht="12" customHeight="1">
       <c r="A155" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B155" s="7">
         <v>21</v>
@@ -16754,7 +16748,7 @@
         <v>107</v>
       </c>
       <c r="E155" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F155" s="3" t="s">
         <v>134</v>
@@ -16780,13 +16774,13 @@
       </c>
       <c r="N155" s="35"/>
       <c r="O155" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q155"/>
     </row>
     <row r="156" spans="1:17" ht="12" customHeight="1">
       <c r="A156" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B156" s="7">
         <v>21</v>
@@ -16798,7 +16792,7 @@
         <v>107</v>
       </c>
       <c r="E156" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>139</v>
@@ -16817,7 +16811,7 @@
         <v>141</v>
       </c>
       <c r="L156" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M156" s="3" t="b">
         <v>1</v>
@@ -16827,7 +16821,7 @@
     </row>
     <row r="157" spans="1:17" ht="12" customHeight="1">
       <c r="A157" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B157" s="7">
         <v>21</v>
@@ -16839,7 +16833,7 @@
         <v>107</v>
       </c>
       <c r="E157" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F157" s="3" t="s">
         <v>139</v>
@@ -16858,7 +16852,7 @@
         <v>141</v>
       </c>
       <c r="L157" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M157" s="3" t="b">
         <v>1</v>
@@ -16868,7 +16862,7 @@
     </row>
     <row r="158" spans="1:17" ht="12" customHeight="1">
       <c r="A158" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B158" s="7">
         <v>21</v>
@@ -16880,7 +16874,7 @@
         <v>107</v>
       </c>
       <c r="E158" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>139</v>
@@ -16899,7 +16893,7 @@
         <v>141</v>
       </c>
       <c r="L158" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M158" s="3" t="b">
         <v>1</v>
@@ -16909,7 +16903,7 @@
     </row>
     <row r="159" spans="1:17" ht="12" customHeight="1">
       <c r="A159" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B159" s="7">
         <v>21</v>
@@ -16921,7 +16915,7 @@
         <v>107</v>
       </c>
       <c r="E159" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F159" s="3" t="s">
         <v>139</v>
@@ -16940,7 +16934,7 @@
         <v>141</v>
       </c>
       <c r="L159" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M159" s="3" t="b">
         <v>1</v>
@@ -16950,7 +16944,7 @@
     </row>
     <row r="160" spans="1:17" ht="12" customHeight="1">
       <c r="A160" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B160" s="7">
         <v>21</v>
@@ -16962,7 +16956,7 @@
         <v>107</v>
       </c>
       <c r="E160" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>139</v>
@@ -16981,7 +16975,7 @@
         <v>141</v>
       </c>
       <c r="L160" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M160" s="3" t="b">
         <v>1</v>
@@ -16991,7 +16985,7 @@
     </row>
     <row r="161" spans="1:17" ht="19.5" customHeight="1">
       <c r="A161" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B161" s="7">
         <v>22</v>
@@ -17003,7 +16997,7 @@
         <v>110</v>
       </c>
       <c r="E161" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F161" s="3" t="s">
         <v>134</v>
@@ -17029,13 +17023,13 @@
       </c>
       <c r="N161" s="35"/>
       <c r="O161" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q161"/>
     </row>
     <row r="162" spans="1:17" ht="12" customHeight="1">
       <c r="A162" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B162" s="7">
         <v>22</v>
@@ -17047,7 +17041,7 @@
         <v>110</v>
       </c>
       <c r="E162" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>134</v>
@@ -17073,13 +17067,13 @@
       </c>
       <c r="N162" s="35"/>
       <c r="O162" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q162"/>
     </row>
     <row r="163" spans="1:17" ht="12" customHeight="1">
       <c r="A163" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B163" s="7">
         <v>22</v>
@@ -17091,7 +17085,7 @@
         <v>110</v>
       </c>
       <c r="E163" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F163" s="3" t="s">
         <v>139</v>
@@ -17110,7 +17104,7 @@
         <v>141</v>
       </c>
       <c r="L163" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M163" s="3" t="b">
         <v>1</v>
@@ -17120,7 +17114,7 @@
     </row>
     <row r="164" spans="1:17" ht="12" customHeight="1">
       <c r="A164" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B164" s="7">
         <v>22</v>
@@ -17132,7 +17126,7 @@
         <v>110</v>
       </c>
       <c r="E164" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>139</v>
@@ -17151,7 +17145,7 @@
         <v>141</v>
       </c>
       <c r="L164" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M164" s="3" t="b">
         <v>1</v>
@@ -17161,7 +17155,7 @@
     </row>
     <row r="165" spans="1:17" ht="12" customHeight="1">
       <c r="A165" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B165" s="7">
         <v>22</v>
@@ -17173,7 +17167,7 @@
         <v>110</v>
       </c>
       <c r="E165" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F165" s="3" t="s">
         <v>139</v>
@@ -17192,7 +17186,7 @@
         <v>141</v>
       </c>
       <c r="L165" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M165" s="3" t="b">
         <v>1</v>
@@ -17202,7 +17196,7 @@
     </row>
     <row r="166" spans="1:17" ht="12" customHeight="1">
       <c r="A166" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B166" s="7">
         <v>22</v>
@@ -17214,7 +17208,7 @@
         <v>110</v>
       </c>
       <c r="E166" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>139</v>
@@ -17233,7 +17227,7 @@
         <v>141</v>
       </c>
       <c r="L166" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M166" s="3" t="b">
         <v>1</v>
@@ -17243,7 +17237,7 @@
     </row>
     <row r="167" spans="1:17" ht="12" customHeight="1">
       <c r="A167" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B167" s="7">
         <v>22</v>
@@ -17255,7 +17249,7 @@
         <v>110</v>
       </c>
       <c r="E167" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F167" s="3" t="s">
         <v>139</v>
@@ -17274,7 +17268,7 @@
         <v>141</v>
       </c>
       <c r="L167" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M167" s="3" t="b">
         <v>1</v>
@@ -17284,7 +17278,7 @@
     </row>
     <row r="168" spans="1:17" ht="19.5" customHeight="1">
       <c r="A168" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B168" s="7">
         <v>23</v>
@@ -17296,7 +17290,7 @@
         <v>114</v>
       </c>
       <c r="E168" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>134</v>
@@ -17322,13 +17316,13 @@
       </c>
       <c r="N168" s="35"/>
       <c r="O168" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="Q168"/>
     </row>
     <row r="169" spans="1:17" ht="12" customHeight="1">
       <c r="A169" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B169" s="7">
         <v>23</v>
@@ -17340,7 +17334,7 @@
         <v>114</v>
       </c>
       <c r="E169" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F169" s="3" t="s">
         <v>134</v>
@@ -17366,13 +17360,13 @@
       </c>
       <c r="N169" s="35"/>
       <c r="O169" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Q169"/>
     </row>
     <row r="170" spans="1:17" ht="12" customHeight="1">
       <c r="A170" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B170" s="7">
         <v>23</v>
@@ -17384,7 +17378,7 @@
         <v>114</v>
       </c>
       <c r="E170" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>139</v>
@@ -17403,7 +17397,7 @@
         <v>141</v>
       </c>
       <c r="L170" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M170" s="3" t="b">
         <v>1</v>
@@ -17413,7 +17407,7 @@
     </row>
     <row r="171" spans="1:17" ht="12" customHeight="1">
       <c r="A171" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B171" s="7">
         <v>23</v>
@@ -17425,7 +17419,7 @@
         <v>114</v>
       </c>
       <c r="E171" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F171" s="3" t="s">
         <v>139</v>
@@ -17444,7 +17438,7 @@
         <v>141</v>
       </c>
       <c r="L171" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M171" s="3" t="b">
         <v>1</v>
@@ -17454,7 +17448,7 @@
     </row>
     <row r="172" spans="1:17" ht="12" customHeight="1">
       <c r="A172" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B172" s="7">
         <v>23</v>
@@ -17466,7 +17460,7 @@
         <v>114</v>
       </c>
       <c r="E172" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>139</v>
@@ -17485,7 +17479,7 @@
         <v>141</v>
       </c>
       <c r="L172" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M172" s="3" t="b">
         <v>1</v>
@@ -17495,7 +17489,7 @@
     </row>
     <row r="173" spans="1:17" ht="12" customHeight="1">
       <c r="A173" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B173" s="7">
         <v>23</v>
@@ -17507,7 +17501,7 @@
         <v>114</v>
       </c>
       <c r="E173" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F173" s="3" t="s">
         <v>139</v>
@@ -17526,7 +17520,7 @@
         <v>141</v>
       </c>
       <c r="L173" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M173" s="3" t="b">
         <v>1</v>
@@ -17536,7 +17530,7 @@
     </row>
     <row r="174" spans="1:17" ht="12" customHeight="1">
       <c r="A174" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B174" s="7">
         <v>23</v>
@@ -17548,7 +17542,7 @@
         <v>114</v>
       </c>
       <c r="E174" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>139</v>
@@ -17567,7 +17561,7 @@
         <v>141</v>
       </c>
       <c r="L174" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M174" s="3" t="b">
         <v>1</v>
@@ -17577,19 +17571,19 @@
     </row>
     <row r="175" spans="1:17" ht="12" customHeight="1">
       <c r="A175" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B175" s="7">
         <v>24</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D175" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E175" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F175" s="3" t="s">
         <v>134</v>
@@ -17615,24 +17609,24 @@
       </c>
       <c r="N175" s="7"/>
       <c r="O175" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="176" spans="1:17" ht="12" customHeight="1">
       <c r="A176" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B176" s="7">
         <v>24</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D176" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E176" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>134</v>
@@ -17658,24 +17652,24 @@
       </c>
       <c r="N176" s="7"/>
       <c r="O176" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="177" spans="1:15" ht="12" customHeight="1">
       <c r="A177" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B177" s="7">
         <v>24</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D177" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E177" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F177" s="3" t="s">
         <v>139</v>
@@ -17694,7 +17688,7 @@
         <v>141</v>
       </c>
       <c r="L177" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M177" s="3" t="b">
         <v>1</v>
@@ -17704,19 +17698,19 @@
     </row>
     <row r="178" spans="1:15" ht="12" customHeight="1">
       <c r="A178" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B178" s="7">
         <v>24</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D178" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E178" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>139</v>
@@ -17735,7 +17729,7 @@
         <v>141</v>
       </c>
       <c r="L178" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M178" s="3" t="b">
         <v>1</v>
@@ -17745,19 +17739,19 @@
     </row>
     <row r="179" spans="1:15" ht="12" customHeight="1">
       <c r="A179" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B179" s="7">
         <v>24</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D179" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E179" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F179" s="3" t="s">
         <v>139</v>
@@ -17776,7 +17770,7 @@
         <v>141</v>
       </c>
       <c r="L179" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M179" s="3" t="b">
         <v>1</v>
@@ -17786,19 +17780,19 @@
     </row>
     <row r="180" spans="1:15" ht="12" customHeight="1">
       <c r="A180" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B180" s="7">
         <v>24</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D180" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E180" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>139</v>
@@ -17817,7 +17811,7 @@
         <v>141</v>
       </c>
       <c r="L180" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M180" s="3" t="b">
         <v>1</v>
@@ -17827,19 +17821,19 @@
     </row>
     <row r="181" spans="1:15" ht="12" customHeight="1">
       <c r="A181" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B181" s="7">
         <v>24</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="D181" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="E181" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F181" s="3" t="s">
         <v>139</v>
@@ -17858,7 +17852,7 @@
         <v>141</v>
       </c>
       <c r="L181" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M181" s="3" t="b">
         <v>1</v>
@@ -17868,19 +17862,19 @@
     </row>
     <row r="182" spans="1:15" ht="12" customHeight="1">
       <c r="A182" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B182" s="7">
         <v>25</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D182" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E182" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>134</v>
@@ -17906,24 +17900,24 @@
       </c>
       <c r="N182" s="7"/>
       <c r="O182" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="183" spans="1:15" ht="12" customHeight="1">
       <c r="A183" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B183" s="7">
         <v>25</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D183" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E183" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F183" s="3" t="s">
         <v>134</v>
@@ -17949,24 +17943,24 @@
       </c>
       <c r="N183" s="7"/>
       <c r="O183" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="184" spans="1:15" ht="12" customHeight="1">
       <c r="A184" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B184" s="7">
         <v>25</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D184" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E184" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>139</v>
@@ -17985,7 +17979,7 @@
         <v>141</v>
       </c>
       <c r="L184" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M184" s="3" t="b">
         <v>1</v>
@@ -17995,19 +17989,19 @@
     </row>
     <row r="185" spans="1:15" ht="12" customHeight="1">
       <c r="A185" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B185" s="7">
         <v>25</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D185" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E185" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F185" s="3" t="s">
         <v>139</v>
@@ -18026,7 +18020,7 @@
         <v>141</v>
       </c>
       <c r="L185" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M185" s="3" t="b">
         <v>1</v>
@@ -18036,19 +18030,19 @@
     </row>
     <row r="186" spans="1:15" ht="12" customHeight="1">
       <c r="A186" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B186" s="7">
         <v>25</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D186" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E186" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>139</v>
@@ -18067,7 +18061,7 @@
         <v>141</v>
       </c>
       <c r="L186" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M186" s="3" t="b">
         <v>1</v>
@@ -18077,19 +18071,19 @@
     </row>
     <row r="187" spans="1:15" ht="12" customHeight="1">
       <c r="A187" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B187" s="7">
         <v>25</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D187" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E187" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F187" s="3" t="s">
         <v>139</v>
@@ -18108,7 +18102,7 @@
         <v>141</v>
       </c>
       <c r="L187" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M187" s="3" t="b">
         <v>1</v>
@@ -18118,19 +18112,19 @@
     </row>
     <row r="188" spans="1:15" ht="12" customHeight="1">
       <c r="A188" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B188" s="7">
         <v>25</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D188" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E188" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>139</v>
@@ -18149,7 +18143,7 @@
         <v>141</v>
       </c>
       <c r="L188" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M188" s="3" t="b">
         <v>1</v>
@@ -18159,19 +18153,19 @@
     </row>
     <row r="189" spans="1:15" ht="12" customHeight="1">
       <c r="A189" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B189" s="7">
         <v>25</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="D189" s="3" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="E189" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F189" s="3" t="s">
         <v>134</v>
@@ -18197,24 +18191,24 @@
       </c>
       <c r="N189" s="7"/>
       <c r="O189" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="190" spans="1:15" ht="12" customHeight="1">
       <c r="A190" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B190" s="7">
         <v>26</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D190" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E190" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>134</v>
@@ -18240,24 +18234,24 @@
       </c>
       <c r="N190" s="7"/>
       <c r="O190" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="191" spans="1:15" ht="12" customHeight="1">
       <c r="A191" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B191" s="7">
         <v>26</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E191" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F191" s="3" t="s">
         <v>139</v>
@@ -18276,7 +18270,7 @@
         <v>141</v>
       </c>
       <c r="L191" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M191" s="3" t="b">
         <v>1</v>
@@ -18286,19 +18280,19 @@
     </row>
     <row r="192" spans="1:15" ht="12" customHeight="1">
       <c r="A192" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B192" s="7">
         <v>26</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D192" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E192" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>139</v>
@@ -18317,7 +18311,7 @@
         <v>141</v>
       </c>
       <c r="L192" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M192" s="3" t="b">
         <v>1</v>
@@ -18327,19 +18321,19 @@
     </row>
     <row r="193" spans="1:15" ht="12" customHeight="1">
       <c r="A193" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B193" s="7">
         <v>26</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D193" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E193" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F193" s="3" t="s">
         <v>139</v>
@@ -18358,7 +18352,7 @@
         <v>141</v>
       </c>
       <c r="L193" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M193" s="3" t="b">
         <v>1</v>
@@ -18368,19 +18362,19 @@
     </row>
     <row r="194" spans="1:15" ht="12" customHeight="1">
       <c r="A194" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B194" s="7">
         <v>26</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D194" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E194" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>139</v>
@@ -18399,7 +18393,7 @@
         <v>141</v>
       </c>
       <c r="L194" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M194" s="3" t="b">
         <v>1</v>
@@ -18409,19 +18403,19 @@
     </row>
     <row r="195" spans="1:15" ht="12" customHeight="1">
       <c r="A195" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B195" s="7">
         <v>26</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D195" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E195" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F195" s="3" t="s">
         <v>139</v>
@@ -18440,7 +18434,7 @@
         <v>141</v>
       </c>
       <c r="L195" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M195" s="3" t="b">
         <v>1</v>
@@ -18450,19 +18444,19 @@
     </row>
     <row r="196" spans="1:15" ht="12" customHeight="1">
       <c r="A196" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B196" s="7">
         <v>26</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="D196" s="3" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="E196" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>134</v>
@@ -18488,24 +18482,24 @@
       </c>
       <c r="N196" s="7"/>
       <c r="O196" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="197" spans="1:15" ht="12" customHeight="1">
       <c r="A197" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B197" s="7">
         <v>27</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D197" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E197" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F197" s="3" t="s">
         <v>134</v>
@@ -18531,24 +18525,24 @@
       </c>
       <c r="N197" s="7"/>
       <c r="O197" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="198" spans="1:15" ht="12" customHeight="1">
       <c r="A198" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B198" s="7">
         <v>27</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D198" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E198" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>139</v>
@@ -18567,7 +18561,7 @@
         <v>141</v>
       </c>
       <c r="L198" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M198" s="3" t="b">
         <v>1</v>
@@ -18577,19 +18571,19 @@
     </row>
     <row r="199" spans="1:15" ht="12" customHeight="1">
       <c r="A199" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B199" s="7">
         <v>27</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D199" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E199" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F199" s="3" t="s">
         <v>139</v>
@@ -18608,7 +18602,7 @@
         <v>141</v>
       </c>
       <c r="L199" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M199" s="3" t="b">
         <v>1</v>
@@ -18618,19 +18612,19 @@
     </row>
     <row r="200" spans="1:15" ht="12" customHeight="1">
       <c r="A200" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B200" s="7">
         <v>27</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D200" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E200" s="3" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>139</v>
@@ -18649,7 +18643,7 @@
         <v>141</v>
       </c>
       <c r="L200" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M200" s="3" t="b">
         <v>1</v>
@@ -18659,19 +18653,19 @@
     </row>
     <row r="201" spans="1:15" ht="12" customHeight="1">
       <c r="A201" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B201" s="7">
         <v>27</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D201" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E201" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F201" s="3" t="s">
         <v>139</v>
@@ -18690,7 +18684,7 @@
         <v>141</v>
       </c>
       <c r="L201" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M201" s="3" t="b">
         <v>1</v>
@@ -18700,19 +18694,19 @@
     </row>
     <row r="202" spans="1:15" ht="12" customHeight="1">
       <c r="A202" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B202" s="7">
         <v>27</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D202" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E202" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>139</v>
@@ -18731,7 +18725,7 @@
         <v>141</v>
       </c>
       <c r="L202" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M202" s="3" t="b">
         <v>1</v>
@@ -18741,19 +18735,19 @@
     </row>
     <row r="203" spans="1:15" ht="12" customHeight="1">
       <c r="A203" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B203" s="7">
         <v>27</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D203" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="E203" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F203" s="3" t="s">
         <v>134</v>
@@ -18779,24 +18773,24 @@
       </c>
       <c r="N203" s="7"/>
       <c r="O203" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="204" spans="1:15" ht="12" customHeight="1">
       <c r="A204" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B204" s="7">
         <v>28</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D204" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E204" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>134</v>
@@ -18822,24 +18816,24 @@
       </c>
       <c r="N204" s="7"/>
       <c r="O204" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="205" spans="1:15" ht="12" customHeight="1">
       <c r="A205" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B205" s="7">
         <v>28</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D205" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E205" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F205" s="3" t="s">
         <v>139</v>
@@ -18858,7 +18852,7 @@
         <v>141</v>
       </c>
       <c r="L205" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M205" s="3" t="b">
         <v>1</v>
@@ -18868,19 +18862,19 @@
     </row>
     <row r="206" spans="1:15" ht="12" customHeight="1">
       <c r="A206" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B206" s="7">
         <v>28</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D206" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E206" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>139</v>
@@ -18899,7 +18893,7 @@
         <v>141</v>
       </c>
       <c r="L206" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M206" s="3" t="b">
         <v>1</v>
@@ -18909,19 +18903,19 @@
     </row>
     <row r="207" spans="1:15" ht="12" customHeight="1">
       <c r="A207" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B207" s="7">
         <v>28</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D207" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E207" s="3" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F207" s="3" t="s">
         <v>139</v>
@@ -18940,7 +18934,7 @@
         <v>141</v>
       </c>
       <c r="L207" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M207" s="3" t="b">
         <v>1</v>
@@ -18950,19 +18944,19 @@
     </row>
     <row r="208" spans="1:15" ht="12" customHeight="1">
       <c r="A208" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B208" s="7">
         <v>28</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D208" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E208" s="3" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>139</v>
@@ -18981,7 +18975,7 @@
         <v>141</v>
       </c>
       <c r="L208" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M208" s="3" t="b">
         <v>1</v>
@@ -18991,19 +18985,19 @@
     </row>
     <row r="209" spans="1:15" ht="12" customHeight="1">
       <c r="A209" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B209" s="7">
         <v>28</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D209" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E209" s="3" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F209" s="3" t="s">
         <v>139</v>
@@ -19022,7 +19016,7 @@
         <v>141</v>
       </c>
       <c r="L209" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M209" s="3" t="b">
         <v>1</v>
@@ -19032,19 +19026,19 @@
     </row>
     <row r="210" spans="1:15" ht="12" customHeight="1">
       <c r="A210" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B210" s="7">
         <v>28</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D210" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E210" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>134</v>
@@ -19070,24 +19064,24 @@
       </c>
       <c r="N210" s="7"/>
       <c r="O210" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="211" spans="1:15" ht="12" customHeight="1">
       <c r="A211" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B211" s="7">
         <v>29</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D211" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E211" s="3" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F211" s="3" t="s">
         <v>134</v>
@@ -19113,24 +19107,24 @@
       </c>
       <c r="N211" s="7"/>
       <c r="O211" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="212" spans="1:15" ht="12" customHeight="1">
       <c r="A212" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B212" s="7">
         <v>29</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D212" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E212" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>139</v>
@@ -19149,7 +19143,7 @@
         <v>141</v>
       </c>
       <c r="L212" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M212" s="3" t="b">
         <v>1</v>
@@ -19159,19 +19153,19 @@
     </row>
     <row r="213" spans="1:15" ht="12" customHeight="1">
       <c r="A213" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B213" s="7">
         <v>29</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D213" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E213" s="3" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F213" s="3" t="s">
         <v>139</v>
@@ -19190,7 +19184,7 @@
         <v>141</v>
       </c>
       <c r="L213" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M213" s="3" t="b">
         <v>1</v>
@@ -19200,19 +19194,19 @@
     </row>
     <row r="214" spans="1:15" ht="12" customHeight="1">
       <c r="A214" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B214" s="7">
         <v>29</v>
       </c>
       <c r="C214" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D214" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E214" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>139</v>
@@ -19231,7 +19225,7 @@
         <v>141</v>
       </c>
       <c r="L214" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M214" s="3" t="b">
         <v>1</v>
@@ -19240,19 +19234,19 @@
     </row>
     <row r="215" spans="1:15" ht="12" customHeight="1">
       <c r="A215" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B215" s="7">
         <v>29</v>
       </c>
       <c r="C215" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D215" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E215" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F215" s="3" t="s">
         <v>139</v>
@@ -19271,7 +19265,7 @@
         <v>141</v>
       </c>
       <c r="L215" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M215" s="3" t="b">
         <v>1</v>
@@ -19280,19 +19274,19 @@
     </row>
     <row r="216" spans="1:15" ht="12" customHeight="1">
       <c r="A216" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B216" s="7">
         <v>29</v>
       </c>
       <c r="C216" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D216" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E216" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>139</v>
@@ -19311,7 +19305,7 @@
         <v>141</v>
       </c>
       <c r="L216" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M216" s="3" t="b">
         <v>1</v>
@@ -19320,19 +19314,19 @@
     </row>
     <row r="217" spans="1:15" ht="12" customHeight="1">
       <c r="A217" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B217" s="7">
         <v>29</v>
       </c>
       <c r="C217" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="D217" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="E217" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F217" s="3" t="s">
         <v>134</v>
@@ -19358,24 +19352,24 @@
       </c>
       <c r="N217" s="7"/>
       <c r="O217" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="218" spans="1:15" ht="12" customHeight="1">
       <c r="A218" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B218" s="7">
         <v>30</v>
       </c>
       <c r="C218" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D218" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E218" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>134</v>
@@ -19401,24 +19395,24 @@
       </c>
       <c r="N218" s="7"/>
       <c r="O218" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="219" spans="1:15" ht="12" customHeight="1">
       <c r="A219" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B219" s="7">
         <v>30</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D219" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E219" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F219" s="3" t="s">
         <v>139</v>
@@ -19437,7 +19431,7 @@
         <v>141</v>
       </c>
       <c r="L219" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M219" s="3" t="b">
         <v>1</v>
@@ -19446,19 +19440,19 @@
     </row>
     <row r="220" spans="1:15" ht="12" customHeight="1">
       <c r="A220" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B220" s="7">
         <v>30</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D220" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E220" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>139</v>
@@ -19477,7 +19471,7 @@
         <v>141</v>
       </c>
       <c r="L220" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M220" s="3" t="b">
         <v>1</v>
@@ -19486,19 +19480,19 @@
     </row>
     <row r="221" spans="1:15" ht="12" customHeight="1">
       <c r="A221" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B221" s="7">
         <v>30</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D221" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E221" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F221" s="3" t="s">
         <v>139</v>
@@ -19517,7 +19511,7 @@
         <v>141</v>
       </c>
       <c r="L221" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M221" s="3" t="b">
         <v>1</v>
@@ -19526,19 +19520,19 @@
     </row>
     <row r="222" spans="1:15" ht="12" customHeight="1">
       <c r="A222" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B222" s="7">
         <v>30</v>
       </c>
       <c r="C222" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D222" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E222" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>139</v>
@@ -19557,7 +19551,7 @@
         <v>141</v>
       </c>
       <c r="L222" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M222" s="3" t="b">
         <v>1</v>
@@ -19566,19 +19560,19 @@
     </row>
     <row r="223" spans="1:15" ht="12" customHeight="1">
       <c r="A223" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B223" s="7">
         <v>30</v>
       </c>
       <c r="C223" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D223" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E223" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F223" s="3" t="s">
         <v>139</v>
@@ -19597,7 +19591,7 @@
         <v>141</v>
       </c>
       <c r="L223" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M223" s="3" t="b">
         <v>1</v>
@@ -19606,19 +19600,19 @@
     </row>
     <row r="224" spans="1:15" ht="12" customHeight="1">
       <c r="A224" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B224" s="7">
         <v>30</v>
       </c>
       <c r="C224" s="3" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D224" s="3" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="E224" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>134</v>
@@ -19644,24 +19638,24 @@
       </c>
       <c r="N224" s="7"/>
       <c r="O224" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="225" spans="1:15" ht="12" customHeight="1">
       <c r="A225" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B225" s="7">
         <v>31</v>
       </c>
       <c r="C225" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D225" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E225" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F225" s="3" t="s">
         <v>134</v>
@@ -19687,24 +19681,24 @@
       </c>
       <c r="N225" s="7"/>
       <c r="O225" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="226" spans="1:15" ht="12" customHeight="1">
       <c r="A226" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B226" s="7">
         <v>31</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D226" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E226" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>139</v>
@@ -19723,7 +19717,7 @@
         <v>141</v>
       </c>
       <c r="L226" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M226" s="3" t="b">
         <v>1</v>
@@ -19732,19 +19726,19 @@
     </row>
     <row r="227" spans="1:15" ht="12" customHeight="1">
       <c r="A227" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B227" s="7">
         <v>31</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E227" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F227" s="3" t="s">
         <v>139</v>
@@ -19763,7 +19757,7 @@
         <v>141</v>
       </c>
       <c r="L227" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M227" s="3" t="b">
         <v>1</v>
@@ -19772,19 +19766,19 @@
     </row>
     <row r="228" spans="1:15" ht="12" customHeight="1">
       <c r="A228" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B228" s="7">
         <v>31</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D228" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E228" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>139</v>
@@ -19803,7 +19797,7 @@
         <v>141</v>
       </c>
       <c r="L228" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M228" s="3" t="b">
         <v>1</v>
@@ -19812,19 +19806,19 @@
     </row>
     <row r="229" spans="1:15" ht="12" customHeight="1">
       <c r="A229" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B229" s="7">
         <v>31</v>
       </c>
       <c r="C229" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D229" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E229" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F229" s="3" t="s">
         <v>139</v>
@@ -19843,7 +19837,7 @@
         <v>141</v>
       </c>
       <c r="L229" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M229" s="3" t="b">
         <v>1</v>
@@ -19852,19 +19846,19 @@
     </row>
     <row r="230" spans="1:15" ht="12" customHeight="1">
       <c r="A230" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B230" s="7">
         <v>31</v>
       </c>
       <c r="C230" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D230" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E230" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>139</v>
@@ -19883,7 +19877,7 @@
         <v>141</v>
       </c>
       <c r="L230" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M230" s="3" t="b">
         <v>1</v>
@@ -19892,19 +19886,19 @@
     </row>
     <row r="231" spans="1:15" ht="12" customHeight="1">
       <c r="A231" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B231" s="7">
         <v>31</v>
       </c>
       <c r="C231" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D231" s="3" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="E231" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F231" s="3" t="s">
         <v>134</v>
@@ -19930,24 +19924,24 @@
       </c>
       <c r="N231" s="7"/>
       <c r="O231" s="57" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
     </row>
     <row r="232" spans="1:15" ht="12" customHeight="1">
       <c r="A232" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B232" s="7">
         <v>32</v>
       </c>
       <c r="C232" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D232" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E232" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>134</v>
@@ -19973,24 +19967,24 @@
       </c>
       <c r="N232" s="7"/>
       <c r="O232" s="57" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
     </row>
     <row r="233" spans="1:15" ht="12" customHeight="1">
       <c r="A233" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B233" s="7">
         <v>32</v>
       </c>
       <c r="C233" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D233" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E233" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="F233" s="3" t="s">
         <v>139</v>
@@ -20009,7 +20003,7 @@
         <v>141</v>
       </c>
       <c r="L233" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M233" s="3" t="b">
         <v>1</v>
@@ -20018,19 +20012,19 @@
     </row>
     <row r="234" spans="1:15" ht="12" customHeight="1">
       <c r="A234" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B234" s="7">
         <v>32</v>
       </c>
       <c r="C234" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D234" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E234" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>139</v>
@@ -20049,7 +20043,7 @@
         <v>141</v>
       </c>
       <c r="L234" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M234" s="3" t="b">
         <v>1</v>
@@ -20058,19 +20052,19 @@
     </row>
     <row r="235" spans="1:15" ht="12" customHeight="1">
       <c r="A235" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B235" s="7">
         <v>32</v>
       </c>
       <c r="C235" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D235" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E235" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F235" s="3" t="s">
         <v>139</v>
@@ -20089,7 +20083,7 @@
         <v>141</v>
       </c>
       <c r="L235" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M235" s="3" t="b">
         <v>1</v>
@@ -20098,19 +20092,19 @@
     </row>
     <row r="236" spans="1:15" ht="12" customHeight="1">
       <c r="A236" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B236" s="7">
         <v>32</v>
       </c>
       <c r="C236" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D236" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E236" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>139</v>
@@ -20129,7 +20123,7 @@
         <v>141</v>
       </c>
       <c r="L236" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M236" s="3" t="b">
         <v>1</v>
@@ -20138,19 +20132,19 @@
     </row>
     <row r="237" spans="1:15" ht="12" customHeight="1">
       <c r="A237" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B237" s="7">
         <v>32</v>
       </c>
       <c r="C237" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D237" s="3" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="E237" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F237" s="3" t="s">
         <v>139</v>
@@ -20169,7 +20163,7 @@
         <v>141</v>
       </c>
       <c r="L237" s="3" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="M237" s="3" t="b">
         <v>1</v>
@@ -22972,7 +22966,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="18.600000000000001" customHeight="1">
       <c r="A1" s="42" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B1" s="39" t="s">
         <v>117</v>
@@ -23002,7 +22996,7 @@
         <v>131</v>
       </c>
       <c r="K1" s="39" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23010,19 +23004,19 @@
         <v>4</v>
       </c>
       <c r="B2" s="40" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C2" s="45" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D2" s="44" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E2" s="41" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F2" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G2" s="45" t="s">
         <v>143</v>
@@ -23031,13 +23025,13 @@
         <v>99</v>
       </c>
       <c r="I2" s="45" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="J2" s="45" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="K2" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23045,22 +23039,22 @@
         <v>5</v>
       </c>
       <c r="B3" s="40" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C3" s="45" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E3" s="40" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="F3" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G3" s="40" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H3" s="40">
         <v>22.5</v>
@@ -23069,10 +23063,10 @@
         <v>30</v>
       </c>
       <c r="J3" s="45" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="K3" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23080,19 +23074,19 @@
         <v>6</v>
       </c>
       <c r="B4" s="40" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C4" s="45" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D4" s="48" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E4" s="40" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F4" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G4" s="43" t="s">
         <v>143</v>
@@ -23104,10 +23098,10 @@
         <v>30</v>
       </c>
       <c r="J4" s="45" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K4" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23115,19 +23109,19 @@
         <v>7</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C5" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D5" s="48" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E5" s="40" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F5" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G5" s="49" t="s">
         <v>143</v>
@@ -23142,7 +23136,7 @@
         <v>42</v>
       </c>
       <c r="K5" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23150,19 +23144,19 @@
         <v>8</v>
       </c>
       <c r="B6" s="40" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C6" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E6" s="41" t="s">
+        <v>351</v>
+      </c>
+      <c r="F6" s="77" t="s">
         <v>354</v>
-      </c>
-      <c r="F6" s="77" t="s">
-        <v>357</v>
       </c>
       <c r="G6" s="43" t="s">
         <v>143</v>
@@ -23174,10 +23168,10 @@
         <v>30</v>
       </c>
       <c r="J6" s="45" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="K6" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23185,19 +23179,19 @@
         <v>11</v>
       </c>
       <c r="B7" s="40" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="C7" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F7" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G7" s="49" t="s">
         <v>143</v>
@@ -23212,7 +23206,7 @@
         <v>42</v>
       </c>
       <c r="K7" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23220,22 +23214,22 @@
         <v>12</v>
       </c>
       <c r="B8" s="40" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C8" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="E8" s="41" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F8" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G8" s="41" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H8" s="78">
         <v>5999</v>
@@ -23244,10 +23238,10 @@
         <v>30</v>
       </c>
       <c r="J8" s="41" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="K8" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23255,17 +23249,17 @@
         <v>13</v>
       </c>
       <c r="B9" s="40" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="C9" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D9" s="47"/>
       <c r="E9" s="40" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F9" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G9" s="49" t="s">
         <v>143</v>
@@ -23277,10 +23271,10 @@
         <v>30</v>
       </c>
       <c r="J9" s="51" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="K9" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23288,17 +23282,17 @@
         <v>14</v>
       </c>
       <c r="B10" s="40" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="C10" s="45" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D10" s="44"/>
       <c r="E10" s="41" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F10" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G10" s="43" t="s">
         <v>143</v>
@@ -23310,10 +23304,10 @@
         <v>30</v>
       </c>
       <c r="J10" s="45" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K10" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23321,17 +23315,17 @@
         <v>15</v>
       </c>
       <c r="B11" s="40" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C11" s="45" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D11" s="47"/>
       <c r="E11" s="40" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F11" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G11" s="49" t="s">
         <v>143</v>
@@ -23342,11 +23336,11 @@
       <c r="I11" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="J11" s="40" t="s">
-        <v>153</v>
+      <c r="J11" s="51" t="s">
+        <v>146</v>
       </c>
       <c r="K11" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23354,17 +23348,17 @@
         <v>18</v>
       </c>
       <c r="B12" s="40" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C12" s="45" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D12" s="44"/>
       <c r="E12" s="50" t="s">
         <v>142</v>
       </c>
       <c r="F12" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G12" s="43" t="s">
         <v>143</v>
@@ -23376,10 +23370,10 @@
         <v>30</v>
       </c>
       <c r="J12" s="51" t="s">
-        <v>144</v>
+        <v>369</v>
       </c>
       <c r="K12" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23387,20 +23381,20 @@
         <v>19</v>
       </c>
       <c r="B13" s="40" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C13" s="45" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="50" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="77" t="s">
+        <v>354</v>
+      </c>
+      <c r="G13" s="40" t="s">
         <v>145</v>
-      </c>
-      <c r="F13" s="77" t="s">
-        <v>357</v>
-      </c>
-      <c r="G13" s="40" t="s">
-        <v>146</v>
       </c>
       <c r="H13" s="50">
         <v>22</v>
@@ -23409,10 +23403,10 @@
         <v>30</v>
       </c>
       <c r="J13" s="51" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="K13" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23420,17 +23414,17 @@
         <v>20</v>
       </c>
       <c r="B14" s="40" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C14" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D14" s="44"/>
       <c r="E14" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F14" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G14" s="43" t="s">
         <v>143</v>
@@ -23442,10 +23436,10 @@
         <v>30</v>
       </c>
       <c r="J14" s="51" t="s">
-        <v>149</v>
+        <v>369</v>
       </c>
       <c r="K14" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23453,17 +23447,17 @@
         <v>21</v>
       </c>
       <c r="B15" s="40" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C15" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D15" s="47"/>
       <c r="E15" s="50" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F15" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G15" s="49" t="s">
         <v>143</v>
@@ -23475,10 +23469,10 @@
         <v>30</v>
       </c>
       <c r="J15" s="45" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K15" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23486,17 +23480,17 @@
         <v>22</v>
       </c>
       <c r="B16" s="40" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C16" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F16" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G16" s="43" t="s">
         <v>143</v>
@@ -23508,10 +23502,10 @@
         <v>30</v>
       </c>
       <c r="J16" s="45" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K16" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="17" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23519,19 +23513,19 @@
         <v>25</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C17" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D17" s="47" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="E17" s="50" t="s">
         <v>142</v>
       </c>
       <c r="F17" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G17" s="49" t="s">
         <v>143</v>
@@ -23543,10 +23537,10 @@
         <v>30</v>
       </c>
       <c r="J17" s="45" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K17" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23554,22 +23548,22 @@
         <v>26</v>
       </c>
       <c r="B18" s="40" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="C18" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D18" s="44" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="E18" s="53" t="s">
+        <v>144</v>
+      </c>
+      <c r="F18" s="77" t="s">
+        <v>354</v>
+      </c>
+      <c r="G18" s="41" t="s">
         <v>145</v>
-      </c>
-      <c r="F18" s="77" t="s">
-        <v>357</v>
-      </c>
-      <c r="G18" s="41" t="s">
-        <v>146</v>
       </c>
       <c r="H18" s="50">
         <v>22</v>
@@ -23581,7 +23575,7 @@
         <v>42</v>
       </c>
       <c r="K18" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23589,17 +23583,17 @@
         <v>27</v>
       </c>
       <c r="B19" s="40" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C19" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D19" s="47"/>
       <c r="E19" s="50" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F19" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G19" s="49" t="s">
         <v>143</v>
@@ -23611,10 +23605,10 @@
         <v>30</v>
       </c>
       <c r="J19" s="45" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="K19" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="20" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23622,17 +23616,17 @@
         <v>28</v>
       </c>
       <c r="B20" s="40" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="C20" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D20" s="44"/>
       <c r="E20" s="55" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F20" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G20" s="43" t="s">
         <v>143</v>
@@ -23644,10 +23638,10 @@
         <v>30</v>
       </c>
       <c r="J20" s="45" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="K20" s="57" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="18.600000000000001" customHeight="1">
@@ -23655,19 +23649,19 @@
         <v>29</v>
       </c>
       <c r="B21" s="40" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="C21" s="45" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D21" s="47" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E21" s="50" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F21" s="77" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="G21" s="49" t="s">
         <v>143</v>
@@ -23679,10 +23673,10 @@
         <v>30</v>
       </c>
       <c r="J21" s="45" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="K21" s="57" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -23754,25 +23748,25 @@
   <sheetData>
     <row r="1" spans="1:9" ht="52.5" customHeight="1">
       <c r="A1" s="28" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="B1" s="61" t="s">
         <v>117</v>
       </c>
       <c r="C1" s="61" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D1" s="61" t="s">
         <v>126</v>
       </c>
       <c r="E1" s="28" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="F1" s="28" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="G1" s="28" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H1" s="29"/>
     </row>
@@ -23781,22 +23775,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="67" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C2" s="69" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D2" s="68" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E2" s="68" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F2" s="70" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G2" s="70" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="H2" s="64"/>
       <c r="I2" s="65"/>
@@ -23806,22 +23800,22 @@
         <v>1</v>
       </c>
       <c r="B3" s="67" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="C3" s="69" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D3" s="68" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="E3" s="68" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F3" s="70" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G3" s="70" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="H3" s="29"/>
     </row>
@@ -23830,22 +23824,22 @@
         <v>1</v>
       </c>
       <c r="B4" s="67" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C4" s="69" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="D4" s="68" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E4" s="68" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F4" s="70" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="G4" s="70" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="12" customHeight="1"/>
@@ -24855,13 +24849,13 @@
   <sheetData>
     <row r="1" spans="1:4" ht="12" customHeight="1">
       <c r="A1" s="29" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="B1" s="29" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="C1" s="29" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D1" s="29" t="s">
         <v>127</v>
@@ -24872,13 +24866,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="29" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="C2" s="57" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D2" s="29" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="12" customHeight="1">
@@ -25951,16 +25945,16 @@
         <v>116</v>
       </c>
       <c r="B1" s="28" t="s">
+        <v>154</v>
+      </c>
+      <c r="C1" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="D1" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="E1" s="28" t="s">
         <v>157</v>
-      </c>
-      <c r="C1" s="28" t="s">
-        <v>158</v>
-      </c>
-      <c r="D1" s="28" t="s">
-        <v>159</v>
-      </c>
-      <c r="E1" s="28" t="s">
-        <v>160</v>
       </c>
       <c r="F1" s="29"/>
     </row>
@@ -25972,7 +25966,7 @@
         <v>26</v>
       </c>
       <c r="C2" s="31" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D2" s="30">
         <v>1</v>
@@ -25984,13 +25978,13 @@
     </row>
     <row r="3" spans="1:6" ht="15.75" customHeight="1">
       <c r="A3" s="30" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="B3" s="30" t="s">
         <v>82</v>
       </c>
       <c r="C3" s="31" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D3" s="30">
         <v>2</v>
